--- a/research/traditional_assets/database/data/malta/malta_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/malta/malta_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0748875544066695</v>
+        <v>0.07465469796624616</v>
       </c>
       <c r="C2">
-        <v>404.3537342877539</v>
+        <v>402.4915597313391</v>
       </c>
       <c r="D2">
-        <v>391.5537342877539</v>
+        <v>394.7135597313391</v>
       </c>
       <c r="E2">
-        <v>-225.3</v>
+        <v>-220.278</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.022</v>
       </c>
       <c r="G2">
         <v>12.8</v>
@@ -1451,28 +1451,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2526066</v>
       </c>
       <c r="N2">
-        <v>44.33333333333333</v>
+        <v>44.08072673333333</v>
       </c>
       <c r="O2">
-        <v>15.51666666666666</v>
+        <v>15.42825435666666</v>
       </c>
       <c r="P2">
-        <v>28.81666666666666</v>
+        <v>28.65247237666667</v>
       </c>
       <c r="Q2">
-        <v>67.81666666666666</v>
+        <v>67.65247237666667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0748875544066695</v>
+        <v>0.07507853329923854</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5362466195717418</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>175.5034640161157</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07465469796624616</v>
+        <v>0.07442184152582282</v>
       </c>
       <c r="C3">
-        <v>402.4915597313391</v>
+        <v>400.6807994561815</v>
       </c>
       <c r="D3">
-        <v>394.7135597313391</v>
+        <v>397.9247994561815</v>
       </c>
       <c r="E3">
-        <v>-220.278</v>
+        <v>-215.256</v>
       </c>
       <c r="F3">
-        <v>5.022</v>
+        <v>10.044</v>
       </c>
       <c r="G3">
         <v>12.8</v>
@@ -1533,28 +1533,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M3">
-        <v>0.2526066</v>
+        <v>0.5052132</v>
       </c>
       <c r="N3">
-        <v>44.08072673333333</v>
+        <v>43.82812013333333</v>
       </c>
       <c r="O3">
-        <v>15.42825435666666</v>
+        <v>15.33984204666666</v>
       </c>
       <c r="P3">
-        <v>28.65247237666667</v>
+        <v>28.48827808666666</v>
       </c>
       <c r="Q3">
-        <v>67.65247237666667</v>
+        <v>67.48827808666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07507853329923854</v>
+        <v>0.07527340972022736</v>
       </c>
       <c r="T3">
-        <v>0.5362466195717418</v>
+        <v>0.5398158496599242</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>175.5034640161157</v>
+        <v>87.75173200805784</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07442184152582282</v>
+        <v>0.07418898508539946</v>
       </c>
       <c r="C4">
-        <v>400.6807994561815</v>
+        <v>398.9227186163349</v>
       </c>
       <c r="D4">
-        <v>397.9247994561815</v>
+        <v>401.1887186163348</v>
       </c>
       <c r="E4">
-        <v>-215.256</v>
+        <v>-210.234</v>
       </c>
       <c r="F4">
-        <v>10.044</v>
+        <v>15.066</v>
       </c>
       <c r="G4">
         <v>12.8</v>
@@ -1615,28 +1615,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M4">
-        <v>0.5052132</v>
+        <v>0.7578197999999999</v>
       </c>
       <c r="N4">
-        <v>43.82812013333333</v>
+        <v>43.57551353333333</v>
       </c>
       <c r="O4">
-        <v>15.33984204666666</v>
+        <v>15.25142973666666</v>
       </c>
       <c r="P4">
-        <v>28.48827808666666</v>
+        <v>28.32408379666666</v>
       </c>
       <c r="Q4">
-        <v>67.48827808666667</v>
+        <v>67.32408379666666</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07527340972022736</v>
+        <v>0.07547230421175202</v>
       </c>
       <c r="T4">
-        <v>0.5398158496599242</v>
+        <v>0.5434586721210588</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>87.75173200805784</v>
+        <v>58.50115467203857</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07418898508539946</v>
+        <v>0.07395612864497612</v>
       </c>
       <c r="C5">
-        <v>398.9227186163349</v>
+        <v>397.2186242180934</v>
       </c>
       <c r="D5">
-        <v>401.1887186163348</v>
+        <v>404.5066242180934</v>
       </c>
       <c r="E5">
-        <v>-210.234</v>
+        <v>-205.212</v>
       </c>
       <c r="F5">
-        <v>15.066</v>
+        <v>20.088</v>
       </c>
       <c r="G5">
         <v>12.8</v>
@@ -1697,28 +1697,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M5">
-        <v>0.7578197999999999</v>
+        <v>1.0104264</v>
       </c>
       <c r="N5">
-        <v>43.57551353333333</v>
+        <v>43.32290693333333</v>
       </c>
       <c r="O5">
-        <v>15.25142973666666</v>
+        <v>15.16301742666666</v>
       </c>
       <c r="P5">
-        <v>28.32408379666666</v>
+        <v>28.15988950666667</v>
       </c>
       <c r="Q5">
-        <v>67.32408379666666</v>
+        <v>67.15988950666667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07547230421175202</v>
+        <v>0.0756753423385168</v>
       </c>
       <c r="T5">
-        <v>0.5434586721210588</v>
+        <v>0.5471773867168005</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.50115467203857</v>
+        <v>43.87586600402892</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07395612864497612</v>
+        <v>0.07372327220455277</v>
       </c>
       <c r="C6">
-        <v>397.2186242180934</v>
+        <v>395.5698668650542</v>
       </c>
       <c r="D6">
-        <v>404.5066242180934</v>
+        <v>407.8798668650542</v>
       </c>
       <c r="E6">
-        <v>-205.212</v>
+        <v>-200.19</v>
       </c>
       <c r="F6">
-        <v>20.088</v>
+        <v>25.11</v>
       </c>
       <c r="G6">
         <v>12.8</v>
@@ -1779,28 +1779,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M6">
-        <v>1.0104264</v>
+        <v>1.263033</v>
       </c>
       <c r="N6">
-        <v>43.32290693333333</v>
+        <v>43.07030033333333</v>
       </c>
       <c r="O6">
-        <v>15.16301742666666</v>
+        <v>15.07460511666666</v>
       </c>
       <c r="P6">
-        <v>28.15988950666667</v>
+        <v>27.99569521666666</v>
       </c>
       <c r="Q6">
-        <v>67.15988950666667</v>
+        <v>66.99569521666666</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0756753423385168</v>
+        <v>0.07588265495216082</v>
       </c>
       <c r="T6">
-        <v>0.5471773867168005</v>
+        <v>0.5509743900408735</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.87586600402892</v>
+        <v>35.10069280322314</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07372327220455277</v>
+        <v>0.07349041576412943</v>
       </c>
       <c r="C7">
-        <v>395.5698668650542</v>
+        <v>393.9778425912251</v>
       </c>
       <c r="D7">
-        <v>407.8798668650542</v>
+        <v>411.309842591225</v>
       </c>
       <c r="E7">
-        <v>-200.19</v>
+        <v>-195.168</v>
       </c>
       <c r="F7">
-        <v>25.11</v>
+        <v>30.132</v>
       </c>
       <c r="G7">
         <v>12.8</v>
@@ -1861,28 +1861,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M7">
-        <v>1.263033</v>
+        <v>1.5156396</v>
       </c>
       <c r="N7">
-        <v>43.07030033333333</v>
+        <v>42.81769373333333</v>
       </c>
       <c r="O7">
-        <v>15.07460511666666</v>
+        <v>14.98619280666666</v>
       </c>
       <c r="P7">
-        <v>27.99569521666666</v>
+        <v>27.83150092666666</v>
       </c>
       <c r="Q7">
-        <v>66.99569521666666</v>
+        <v>66.83150092666666</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07588265495216082</v>
+        <v>0.07609437847247813</v>
       </c>
       <c r="T7">
-        <v>0.5509743900408735</v>
+        <v>0.554852180669714</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.10069280322314</v>
+        <v>29.25057733601928</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07349041576412943</v>
+        <v>0.0732575593237061</v>
       </c>
       <c r="C8">
-        <v>393.9778425912251</v>
+        <v>392.4439947874102</v>
       </c>
       <c r="D8">
-        <v>411.309842591225</v>
+        <v>414.7979947874102</v>
       </c>
       <c r="E8">
-        <v>-195.168</v>
+        <v>-190.146</v>
       </c>
       <c r="F8">
-        <v>30.132</v>
+        <v>35.154</v>
       </c>
       <c r="G8">
         <v>12.8</v>
@@ -1943,28 +1943,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M8">
-        <v>1.5156396</v>
+        <v>1.7682462</v>
       </c>
       <c r="N8">
-        <v>42.81769373333333</v>
+        <v>42.56508713333333</v>
       </c>
       <c r="O8">
-        <v>14.98619280666666</v>
+        <v>14.89778049666666</v>
       </c>
       <c r="P8">
-        <v>27.83150092666666</v>
+        <v>27.66730663666667</v>
       </c>
       <c r="Q8">
-        <v>66.83150092666666</v>
+        <v>66.66730663666667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07609437847247813</v>
+        <v>0.07631065518678075</v>
       </c>
       <c r="T8">
-        <v>0.554852180669714</v>
+        <v>0.5588133646454113</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.25057733601928</v>
+        <v>25.07192343087367</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07325755932370609</v>
+        <v>0.07302470288328275</v>
       </c>
       <c r="C9">
-        <v>392.4439947874105</v>
+        <v>390.9698162264553</v>
       </c>
       <c r="D9">
-        <v>414.7979947874105</v>
+        <v>418.3458162264553</v>
       </c>
       <c r="E9">
-        <v>-190.146</v>
+        <v>-185.124</v>
       </c>
       <c r="F9">
-        <v>35.154</v>
+        <v>40.176</v>
       </c>
       <c r="G9">
         <v>12.8</v>
@@ -2025,28 +2025,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M9">
-        <v>1.7682462</v>
+        <v>2.0208528</v>
       </c>
       <c r="N9">
-        <v>42.56508713333333</v>
+        <v>42.31248053333333</v>
       </c>
       <c r="O9">
-        <v>14.89778049666666</v>
+        <v>14.80936818666666</v>
       </c>
       <c r="P9">
-        <v>27.66730663666667</v>
+        <v>27.50311234666666</v>
       </c>
       <c r="Q9">
-        <v>66.66730663666667</v>
+        <v>66.50311234666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07631065518678075</v>
+        <v>0.0765316335687856</v>
       </c>
       <c r="T9">
-        <v>0.5588133646454113</v>
+        <v>0.5628606613162325</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.07192343087367</v>
+        <v>21.93793300201446</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07302470288328275</v>
+        <v>0.07279184644285941</v>
       </c>
       <c r="C10">
-        <v>390.9698162264553</v>
+        <v>389.5568511933188</v>
       </c>
       <c r="D10">
-        <v>418.3458162264553</v>
+        <v>421.9548511933187</v>
       </c>
       <c r="E10">
-        <v>-185.124</v>
+        <v>-180.102</v>
       </c>
       <c r="F10">
-        <v>40.176</v>
+        <v>45.198</v>
       </c>
       <c r="G10">
         <v>12.8</v>
@@ -2107,28 +2107,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M10">
-        <v>2.0208528</v>
+        <v>2.2734594</v>
       </c>
       <c r="N10">
-        <v>42.31248053333333</v>
+        <v>42.05987393333333</v>
       </c>
       <c r="O10">
-        <v>14.80936818666666</v>
+        <v>14.72095587666666</v>
       </c>
       <c r="P10">
-        <v>27.50311234666666</v>
+        <v>27.33891805666666</v>
       </c>
       <c r="Q10">
-        <v>66.50311234666667</v>
+        <v>66.33891805666667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0765316335687856</v>
+        <v>0.07675746861852682</v>
       </c>
       <c r="T10">
-        <v>0.5628606613162325</v>
+        <v>0.5669969095622366</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.93793300201446</v>
+        <v>19.50038489067952</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07279184644285941</v>
+        <v>0.07255899000243607</v>
       </c>
       <c r="C11">
-        <v>389.5568511933188</v>
+        <v>388.206697726364</v>
       </c>
       <c r="D11">
-        <v>421.9548511933187</v>
+        <v>425.626697726364</v>
       </c>
       <c r="E11">
-        <v>-180.102</v>
+        <v>-175.08</v>
       </c>
       <c r="F11">
-        <v>45.198</v>
+        <v>50.21999999999999</v>
       </c>
       <c r="G11">
         <v>12.8</v>
@@ -2189,28 +2189,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M11">
-        <v>2.2734594</v>
+        <v>2.526065999999999</v>
       </c>
       <c r="N11">
-        <v>42.05987393333333</v>
+        <v>41.80726733333333</v>
       </c>
       <c r="O11">
-        <v>14.72095587666666</v>
+        <v>14.63254356666666</v>
       </c>
       <c r="P11">
-        <v>27.33891805666666</v>
+        <v>27.17472376666667</v>
       </c>
       <c r="Q11">
-        <v>66.33891805666667</v>
+        <v>66.17472376666666</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07675746861852682</v>
+        <v>0.07698832222492896</v>
       </c>
       <c r="T11">
-        <v>0.5669969095622366</v>
+        <v>0.5712250744359296</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.50038489067952</v>
+        <v>17.55034640161157</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07255899000243607</v>
+        <v>0.07232613356201271</v>
       </c>
       <c r="C12">
-        <v>388.206697726364</v>
+        <v>386.9210099766966</v>
       </c>
       <c r="D12">
-        <v>425.626697726364</v>
+        <v>429.3630099766966</v>
       </c>
       <c r="E12">
-        <v>-175.08</v>
+        <v>-170.058</v>
       </c>
       <c r="F12">
-        <v>50.22</v>
+        <v>55.242</v>
       </c>
       <c r="G12">
         <v>12.8</v>
@@ -2271,28 +2271,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M12">
-        <v>2.526066</v>
+        <v>2.7786726</v>
       </c>
       <c r="N12">
-        <v>41.80726733333333</v>
+        <v>41.55466073333333</v>
       </c>
       <c r="O12">
-        <v>14.63254356666666</v>
+        <v>14.54413125666666</v>
       </c>
       <c r="P12">
-        <v>27.17472376666667</v>
+        <v>27.01052947666667</v>
       </c>
       <c r="Q12">
-        <v>66.17472376666666</v>
+        <v>66.01052947666666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07698832222492896</v>
+        <v>0.07722436355282328</v>
       </c>
       <c r="T12">
-        <v>0.5712250744359296</v>
+        <v>0.5755482542506045</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.55034640161157</v>
+        <v>15.95486036510143</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07232613356201271</v>
+        <v>0.07209327712158939</v>
       </c>
       <c r="C13">
-        <v>386.9210099766966</v>
+        <v>385.70150069287</v>
       </c>
       <c r="D13">
-        <v>429.3630099766966</v>
+        <v>433.16550069287</v>
       </c>
       <c r="E13">
-        <v>-170.058</v>
+        <v>-165.036</v>
       </c>
       <c r="F13">
-        <v>55.242</v>
+        <v>60.264</v>
       </c>
       <c r="G13">
         <v>12.8</v>
@@ -2353,28 +2353,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M13">
-        <v>2.7786726</v>
+        <v>3.0312792</v>
       </c>
       <c r="N13">
-        <v>41.55466073333333</v>
+        <v>41.30205413333333</v>
       </c>
       <c r="O13">
-        <v>14.54413125666666</v>
+        <v>14.45571894666666</v>
       </c>
       <c r="P13">
-        <v>27.01052947666667</v>
+        <v>26.84633518666666</v>
       </c>
       <c r="Q13">
-        <v>66.01052947666666</v>
+        <v>65.84633518666666</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07722436355282328</v>
+        <v>0.07746576945635157</v>
       </c>
       <c r="T13">
-        <v>0.5755482542506045</v>
+        <v>0.5799696881519766</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.95486036510143</v>
+        <v>14.62528866800964</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07209327712158939</v>
+        <v>0.07186042068116603</v>
       </c>
       <c r="C14">
-        <v>385.70150069287</v>
+        <v>384.5499438388027</v>
       </c>
       <c r="D14">
-        <v>433.16550069287</v>
+        <v>437.0359438388027</v>
       </c>
       <c r="E14">
-        <v>-165.036</v>
+        <v>-160.014</v>
       </c>
       <c r="F14">
-        <v>60.264</v>
+        <v>65.286</v>
       </c>
       <c r="G14">
         <v>12.8</v>
@@ -2435,28 +2435,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M14">
-        <v>3.0312792</v>
+        <v>3.2838858</v>
       </c>
       <c r="N14">
-        <v>41.30205413333333</v>
+        <v>41.04944753333333</v>
       </c>
       <c r="O14">
-        <v>14.45571894666666</v>
+        <v>14.36730663666666</v>
       </c>
       <c r="P14">
-        <v>26.84633518666666</v>
+        <v>26.68214089666667</v>
       </c>
       <c r="Q14">
-        <v>65.84633518666666</v>
+        <v>65.68214089666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07746576945635157</v>
+        <v>0.07771272492088049</v>
       </c>
       <c r="T14">
-        <v>0.5799696881519766</v>
+        <v>0.5844927642120008</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.62528866800964</v>
+        <v>13.50026646277813</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07186042068116603</v>
+        <v>0.07176406424074269</v>
       </c>
       <c r="C15">
-        <v>384.5499438388027</v>
+        <v>381.1498481560507</v>
       </c>
       <c r="D15">
-        <v>437.0359438388027</v>
+        <v>438.6578481560506</v>
       </c>
       <c r="E15">
-        <v>-160.014</v>
+        <v>-154.992</v>
       </c>
       <c r="F15">
-        <v>65.286</v>
+        <v>70.30800000000001</v>
       </c>
       <c r="G15">
         <v>12.8</v>
@@ -2517,45 +2517,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M15">
-        <v>3.2838858</v>
+        <v>3.6419544</v>
       </c>
       <c r="N15">
-        <v>41.04944753333333</v>
+        <v>40.69137893333333</v>
       </c>
       <c r="O15">
-        <v>14.36730663666666</v>
+        <v>14.24198262666666</v>
       </c>
       <c r="P15">
-        <v>26.68214089666667</v>
+        <v>26.44939630666666</v>
       </c>
       <c r="Q15">
-        <v>65.68214089666667</v>
+        <v>65.44939630666667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07771272492088049</v>
+        <v>0.07796542353574731</v>
       </c>
       <c r="T15">
-        <v>0.5844927642120008</v>
+        <v>0.5891210280873747</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.50026646277813</v>
+        <v>12.1729512410516</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07176406424074269</v>
+        <v>0.07154095780031935</v>
       </c>
       <c r="C16">
-        <v>381.1498481560507</v>
+        <v>379.9298586260978</v>
       </c>
       <c r="D16">
-        <v>438.6578481560506</v>
+        <v>442.4598586260978</v>
       </c>
       <c r="E16">
-        <v>-154.992</v>
+        <v>-149.97</v>
       </c>
       <c r="F16">
-        <v>70.30800000000001</v>
+        <v>75.33000000000001</v>
       </c>
       <c r="G16">
         <v>12.8</v>
@@ -2599,28 +2599,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M16">
-        <v>3.6419544</v>
+        <v>3.902094</v>
       </c>
       <c r="N16">
-        <v>40.69137893333333</v>
+        <v>40.43123933333333</v>
       </c>
       <c r="O16">
-        <v>14.24198262666666</v>
+        <v>14.15093376666666</v>
       </c>
       <c r="P16">
-        <v>26.44939630666666</v>
+        <v>26.28030556666667</v>
       </c>
       <c r="Q16">
-        <v>65.44939630666667</v>
+        <v>65.28030556666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07796542353574731</v>
+        <v>0.07822406800037571</v>
       </c>
       <c r="T16">
-        <v>0.5891210280873747</v>
+        <v>0.5938581922892276</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.1729512410516</v>
+        <v>11.36142115831482</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07154095780031935</v>
+        <v>0.071317851359896</v>
       </c>
       <c r="C17">
-        <v>379.9298586260978</v>
+        <v>378.7763522032425</v>
       </c>
       <c r="D17">
-        <v>442.4598586260978</v>
+        <v>446.3283522032424</v>
       </c>
       <c r="E17">
-        <v>-149.97</v>
+        <v>-144.948</v>
       </c>
       <c r="F17">
-        <v>75.33</v>
+        <v>80.352</v>
       </c>
       <c r="G17">
         <v>12.8</v>
@@ -2681,28 +2681,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M17">
-        <v>3.902094</v>
+        <v>4.1622336</v>
       </c>
       <c r="N17">
-        <v>40.43123933333333</v>
+        <v>40.17109973333333</v>
       </c>
       <c r="O17">
-        <v>14.15093376666666</v>
+        <v>14.05988490666666</v>
       </c>
       <c r="P17">
-        <v>26.28030556666667</v>
+        <v>26.11121482666666</v>
       </c>
       <c r="Q17">
-        <v>65.28030556666667</v>
+        <v>65.11121482666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07822406800037571</v>
+        <v>0.07848887066654286</v>
       </c>
       <c r="T17">
-        <v>0.5938581922892276</v>
+        <v>0.5987081461149344</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.36142115831483</v>
+        <v>10.65133233592015</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.071317851359896</v>
+        <v>0.07109474491947267</v>
       </c>
       <c r="C18">
-        <v>378.7763522032425</v>
+        <v>377.6910880840388</v>
       </c>
       <c r="D18">
-        <v>446.3283522032424</v>
+        <v>450.2650880840388</v>
       </c>
       <c r="E18">
-        <v>-144.948</v>
+        <v>-139.926</v>
       </c>
       <c r="F18">
-        <v>80.352</v>
+        <v>85.37400000000001</v>
       </c>
       <c r="G18">
         <v>12.8</v>
@@ -2763,28 +2763,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M18">
-        <v>4.1622336</v>
+        <v>4.4223732</v>
       </c>
       <c r="N18">
-        <v>40.17109973333333</v>
+        <v>39.91096013333333</v>
       </c>
       <c r="O18">
-        <v>14.05988490666666</v>
+        <v>13.96883604666666</v>
       </c>
       <c r="P18">
-        <v>26.11121482666666</v>
+        <v>25.94212408666666</v>
       </c>
       <c r="Q18">
-        <v>65.11121482666667</v>
+        <v>64.94212408666667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07848887066654286</v>
+        <v>0.07876005411984659</v>
       </c>
       <c r="T18">
-        <v>0.5987081461149344</v>
+        <v>0.6036749662978871</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.65133233592015</v>
+        <v>10.02478337498367</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07109474491947267</v>
+        <v>0.07107053847904932</v>
       </c>
       <c r="C19">
-        <v>377.6910880840388</v>
+        <v>373.1003932989418</v>
       </c>
       <c r="D19">
-        <v>450.2650880840388</v>
+        <v>450.6963932989418</v>
       </c>
       <c r="E19">
-        <v>-139.926</v>
+        <v>-134.904</v>
       </c>
       <c r="F19">
-        <v>85.37400000000001</v>
+        <v>90.39600000000002</v>
       </c>
       <c r="G19">
         <v>12.8</v>
@@ -2845,45 +2845,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M19">
-        <v>4.4223732</v>
+        <v>4.836186000000001</v>
       </c>
       <c r="N19">
-        <v>39.91096013333333</v>
+        <v>39.49714733333333</v>
       </c>
       <c r="O19">
-        <v>13.96883604666666</v>
+        <v>13.82400156666666</v>
       </c>
       <c r="P19">
-        <v>25.94212408666666</v>
+        <v>25.67314576666666</v>
       </c>
       <c r="Q19">
-        <v>64.94212408666667</v>
+        <v>64.67314576666666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07876005411984659</v>
+        <v>0.07903785180371868</v>
       </c>
       <c r="T19">
-        <v>0.6036749662978871</v>
+        <v>0.6087629284365215</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.02478337498367</v>
+        <v>9.167003364497008</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07107053847904933</v>
+        <v>0.07085848203862598</v>
       </c>
       <c r="C20">
-        <v>373.1003932989415</v>
+        <v>371.8923941920242</v>
       </c>
       <c r="D20">
-        <v>450.6963932989415</v>
+        <v>454.5103941920242</v>
       </c>
       <c r="E20">
-        <v>-134.904</v>
+        <v>-129.882</v>
       </c>
       <c r="F20">
-        <v>90.396</v>
+        <v>95.41799999999999</v>
       </c>
       <c r="G20">
         <v>12.8</v>
@@ -2927,28 +2927,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M20">
-        <v>4.836186</v>
+        <v>5.104862999999999</v>
       </c>
       <c r="N20">
-        <v>39.49714733333333</v>
+        <v>39.22847033333333</v>
       </c>
       <c r="O20">
-        <v>13.82400156666666</v>
+        <v>13.72996461666666</v>
       </c>
       <c r="P20">
-        <v>25.67314576666666</v>
+        <v>25.49850571666666</v>
       </c>
       <c r="Q20">
-        <v>64.67314576666666</v>
+        <v>64.49850571666667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07903785180371868</v>
+        <v>0.0793225086896617</v>
       </c>
       <c r="T20">
-        <v>0.6087629284365215</v>
+        <v>0.613976519269937</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.16700336449701</v>
+        <v>8.684529503207692</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07085848203862598</v>
+        <v>0.07064642559820265</v>
       </c>
       <c r="C21">
-        <v>371.8923941920242</v>
+        <v>370.7494976850729</v>
       </c>
       <c r="D21">
-        <v>454.5103941920242</v>
+        <v>458.3894976850729</v>
       </c>
       <c r="E21">
-        <v>-129.882</v>
+        <v>-124.86</v>
       </c>
       <c r="F21">
-        <v>95.41799999999999</v>
+        <v>100.44</v>
       </c>
       <c r="G21">
         <v>12.8</v>
@@ -3009,28 +3009,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M21">
-        <v>5.104862999999999</v>
+        <v>5.37354</v>
       </c>
       <c r="N21">
-        <v>39.22847033333333</v>
+        <v>38.95979333333333</v>
       </c>
       <c r="O21">
-        <v>13.72996461666666</v>
+        <v>13.63592766666667</v>
       </c>
       <c r="P21">
-        <v>25.49850571666666</v>
+        <v>25.32386566666666</v>
       </c>
       <c r="Q21">
-        <v>64.49850571666667</v>
+        <v>64.32386566666666</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0793225086896617</v>
+        <v>0.07961428199775331</v>
       </c>
       <c r="T21">
-        <v>0.613976519269937</v>
+        <v>0.619320449874188</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.684529503207692</v>
+        <v>8.250303028047307</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07064642559820265</v>
+        <v>0.0704343691577793</v>
       </c>
       <c r="C22">
-        <v>370.7494976850729</v>
+        <v>369.673385017684</v>
       </c>
       <c r="D22">
-        <v>458.3894976850729</v>
+        <v>462.335385017684</v>
       </c>
       <c r="E22">
-        <v>-124.86</v>
+        <v>-119.838</v>
       </c>
       <c r="F22">
-        <v>100.44</v>
+        <v>105.462</v>
       </c>
       <c r="G22">
         <v>12.8</v>
@@ -3091,28 +3091,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M22">
-        <v>5.37354</v>
+        <v>5.642217</v>
       </c>
       <c r="N22">
-        <v>38.95979333333333</v>
+        <v>38.69111633333333</v>
       </c>
       <c r="O22">
-        <v>13.63592766666667</v>
+        <v>13.54189071666666</v>
       </c>
       <c r="P22">
-        <v>25.32386566666666</v>
+        <v>25.14922561666666</v>
       </c>
       <c r="Q22">
-        <v>64.32386566666666</v>
+        <v>64.14922561666666</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07961428199775331</v>
+        <v>0.07991344197187253</v>
       </c>
       <c r="T22">
-        <v>0.619320449874188</v>
+        <v>0.624799669860825</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.250303028047307</v>
+        <v>7.857431455283149</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0704343691577793</v>
+        <v>0.07033671271735595</v>
       </c>
       <c r="C23">
-        <v>369.673385017684</v>
+        <v>366.4914859514432</v>
       </c>
       <c r="D23">
-        <v>462.335385017684</v>
+        <v>464.1754859514431</v>
       </c>
       <c r="E23">
-        <v>-119.838</v>
+        <v>-114.816</v>
       </c>
       <c r="F23">
-        <v>105.462</v>
+        <v>110.484</v>
       </c>
       <c r="G23">
         <v>12.8</v>
@@ -3173,45 +3173,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M23">
-        <v>5.642217</v>
+        <v>5.9992812</v>
       </c>
       <c r="N23">
-        <v>38.69111633333333</v>
+        <v>38.33405213333333</v>
       </c>
       <c r="O23">
-        <v>13.54189071666666</v>
+        <v>13.41691824666666</v>
       </c>
       <c r="P23">
-        <v>25.14922561666666</v>
+        <v>24.91713388666667</v>
       </c>
       <c r="Q23">
-        <v>64.14922561666666</v>
+        <v>63.91713388666666</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07991344197187253</v>
+        <v>0.08022027271455891</v>
       </c>
       <c r="T23">
-        <v>0.624799669860825</v>
+        <v>0.6304193826676322</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.85743145528315</v>
+        <v>7.389774183836113</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07033671271735595</v>
+        <v>0.07012985627693261</v>
       </c>
       <c r="C24">
-        <v>366.4914859514432</v>
+        <v>365.4159822916918</v>
       </c>
       <c r="D24">
-        <v>464.1754859514431</v>
+        <v>468.1219822916918</v>
       </c>
       <c r="E24">
-        <v>-114.816</v>
+        <v>-109.794</v>
       </c>
       <c r="F24">
-        <v>110.484</v>
+        <v>115.506</v>
       </c>
       <c r="G24">
         <v>12.8</v>
@@ -3255,28 +3255,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M24">
-        <v>5.9992812</v>
+        <v>6.2719758</v>
       </c>
       <c r="N24">
-        <v>38.33405213333333</v>
+        <v>38.06135753333333</v>
       </c>
       <c r="O24">
-        <v>13.41691824666666</v>
+        <v>13.32147513666667</v>
       </c>
       <c r="P24">
-        <v>24.91713388666667</v>
+        <v>24.73988239666667</v>
       </c>
       <c r="Q24">
-        <v>63.91713388666666</v>
+        <v>63.73988239666667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08022027271455891</v>
+        <v>0.08053507308692547</v>
       </c>
       <c r="T24">
-        <v>0.6304193826676322</v>
+        <v>0.63618506204085</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.389774183836113</v>
+        <v>7.068479654104107</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07012985627693261</v>
+        <v>0.06992299983650926</v>
       </c>
       <c r="C25">
-        <v>365.4159822916918</v>
+        <v>364.4081616059172</v>
       </c>
       <c r="D25">
-        <v>468.1219822916918</v>
+        <v>472.1361616059172</v>
       </c>
       <c r="E25">
-        <v>-109.794</v>
+        <v>-104.772</v>
       </c>
       <c r="F25">
-        <v>115.506</v>
+        <v>120.528</v>
       </c>
       <c r="G25">
         <v>12.8</v>
@@ -3337,28 +3337,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M25">
-        <v>6.2719758</v>
+        <v>6.5446704</v>
       </c>
       <c r="N25">
-        <v>38.06135753333333</v>
+        <v>37.78866293333333</v>
       </c>
       <c r="O25">
-        <v>13.32147513666667</v>
+        <v>13.22603202666666</v>
       </c>
       <c r="P25">
-        <v>24.73988239666667</v>
+        <v>24.56263090666666</v>
       </c>
       <c r="Q25">
-        <v>63.73988239666667</v>
+        <v>63.56263090666666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08053507308692547</v>
+        <v>0.08085815767961745</v>
       </c>
       <c r="T25">
-        <v>0.63618506204085</v>
+        <v>0.6421024698186261</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.068479654104107</v>
+        <v>6.773959668516436</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06992299983650925</v>
+        <v>0.06971614339608592</v>
       </c>
       <c r="C26">
-        <v>364.4081616059175</v>
+        <v>363.4697801127757</v>
       </c>
       <c r="D26">
-        <v>472.1361616059174</v>
+        <v>476.2197801127757</v>
       </c>
       <c r="E26">
-        <v>-104.772</v>
+        <v>-99.75000000000001</v>
       </c>
       <c r="F26">
-        <v>120.528</v>
+        <v>125.55</v>
       </c>
       <c r="G26">
         <v>12.8</v>
@@ -3419,28 +3419,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M26">
-        <v>6.544670399999999</v>
+        <v>6.817365</v>
       </c>
       <c r="N26">
-        <v>37.78866293333333</v>
+        <v>37.51596833333333</v>
       </c>
       <c r="O26">
-        <v>13.22603202666666</v>
+        <v>13.13058891666666</v>
       </c>
       <c r="P26">
-        <v>24.56263090666666</v>
+        <v>24.38537941666666</v>
       </c>
       <c r="Q26">
-        <v>63.56263090666666</v>
+        <v>63.38537941666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08085815767961745</v>
+        <v>0.08118985786144789</v>
       </c>
       <c r="T26">
-        <v>0.6421024698186261</v>
+        <v>0.648177675137143</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.773959668516436</v>
+        <v>6.503001281775778</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06971614339608592</v>
+        <v>0.06950928695566258</v>
       </c>
       <c r="C27">
-        <v>363.4697801127757</v>
+        <v>362.6026553208549</v>
       </c>
       <c r="D27">
-        <v>476.2197801127757</v>
+        <v>480.3746553208549</v>
       </c>
       <c r="E27">
-        <v>-99.75000000000001</v>
+        <v>-94.72800000000001</v>
       </c>
       <c r="F27">
-        <v>125.55</v>
+        <v>130.572</v>
       </c>
       <c r="G27">
         <v>12.8</v>
@@ -3501,28 +3501,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M27">
-        <v>6.817365</v>
+        <v>7.0900596</v>
       </c>
       <c r="N27">
-        <v>37.51596833333333</v>
+        <v>37.24327373333333</v>
       </c>
       <c r="O27">
-        <v>13.13058891666666</v>
+        <v>13.03514580666666</v>
       </c>
       <c r="P27">
-        <v>24.38537941666666</v>
+        <v>24.20812792666666</v>
       </c>
       <c r="Q27">
-        <v>63.38537941666667</v>
+        <v>63.20812792666666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08118985786144789</v>
+        <v>0.08153052291305754</v>
       </c>
       <c r="T27">
-        <v>0.648177675137143</v>
+        <v>0.6544170751939981</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.503001281775778</v>
+        <v>6.252885847861325</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06950928695566258</v>
+        <v>0.06947793051523923</v>
       </c>
       <c r="C28">
-        <v>362.6026553208549</v>
+        <v>358.2168105477975</v>
       </c>
       <c r="D28">
-        <v>480.3746553208549</v>
+        <v>481.0108105477975</v>
       </c>
       <c r="E28">
-        <v>-94.72800000000001</v>
+        <v>-89.70600000000002</v>
       </c>
       <c r="F28">
-        <v>130.572</v>
+        <v>135.594</v>
       </c>
       <c r="G28">
         <v>12.8</v>
@@ -3583,45 +3583,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M28">
-        <v>7.0900596</v>
+        <v>7.4983482</v>
       </c>
       <c r="N28">
-        <v>37.24327373333333</v>
+        <v>36.83498513333333</v>
       </c>
       <c r="O28">
-        <v>13.03514580666666</v>
+        <v>12.89224479666666</v>
       </c>
       <c r="P28">
-        <v>24.20812792666666</v>
+        <v>23.94274033666666</v>
       </c>
       <c r="Q28">
-        <v>63.20812792666666</v>
+        <v>62.94274033666666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08153052291305754</v>
+        <v>0.08188052125375236</v>
       </c>
       <c r="T28">
-        <v>0.6544170751939981</v>
+        <v>0.6608274177181643</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.252885847861325</v>
+        <v>5.912413261007715</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06947793051523923</v>
+        <v>0.06927757407481588</v>
       </c>
       <c r="C29">
-        <v>358.2168105477975</v>
+        <v>357.2997326960311</v>
       </c>
       <c r="D29">
-        <v>481.0108105477975</v>
+        <v>485.1157326960311</v>
       </c>
       <c r="E29">
-        <v>-89.70600000000002</v>
+        <v>-84.684</v>
       </c>
       <c r="F29">
-        <v>135.594</v>
+        <v>140.616</v>
       </c>
       <c r="G29">
         <v>12.8</v>
@@ -3665,28 +3665,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M29">
-        <v>7.4983482</v>
+        <v>7.776064800000001</v>
       </c>
       <c r="N29">
-        <v>36.83498513333333</v>
+        <v>36.55726853333333</v>
       </c>
       <c r="O29">
-        <v>12.89224479666666</v>
+        <v>12.79504398666666</v>
       </c>
       <c r="P29">
-        <v>23.94274033666666</v>
+        <v>23.76222454666667</v>
       </c>
       <c r="Q29">
-        <v>62.94274033666666</v>
+        <v>62.76222454666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08188052125375236</v>
+        <v>0.08224024177057762</v>
       </c>
       <c r="T29">
-        <v>0.6608274177181643</v>
+        <v>0.6674158253124463</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.912413261007715</v>
+        <v>5.701255644543153</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06927757407481588</v>
+        <v>0.06907721763439253</v>
       </c>
       <c r="C30">
-        <v>357.2997326960311</v>
+        <v>356.4533202994538</v>
       </c>
       <c r="D30">
-        <v>485.1157326960311</v>
+        <v>489.2913202994538</v>
       </c>
       <c r="E30">
-        <v>-84.684</v>
+        <v>-79.66200000000001</v>
       </c>
       <c r="F30">
-        <v>140.616</v>
+        <v>145.638</v>
       </c>
       <c r="G30">
         <v>12.8</v>
@@ -3747,28 +3747,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M30">
-        <v>7.776064800000001</v>
+        <v>8.0537814</v>
       </c>
       <c r="N30">
-        <v>36.55726853333333</v>
+        <v>36.27955193333333</v>
       </c>
       <c r="O30">
-        <v>12.79504398666666</v>
+        <v>12.69784317666666</v>
       </c>
       <c r="P30">
-        <v>23.76222454666667</v>
+        <v>23.58170875666666</v>
       </c>
       <c r="Q30">
-        <v>62.76222454666667</v>
+        <v>62.58170875666666</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08224024177057762</v>
+        <v>0.08261009525970781</v>
       </c>
       <c r="T30">
-        <v>0.6674158253124463</v>
+        <v>0.674189821853046</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.701255644543153</v>
+        <v>5.504660622317528</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06907721763439253</v>
+        <v>0.0688768611939692</v>
       </c>
       <c r="C31">
-        <v>356.4533202994538</v>
+        <v>355.6794139392792</v>
       </c>
       <c r="D31">
-        <v>489.2913202994538</v>
+        <v>493.5394139392792</v>
       </c>
       <c r="E31">
-        <v>-79.66200000000003</v>
+        <v>-74.64000000000001</v>
       </c>
       <c r="F31">
-        <v>145.638</v>
+        <v>150.66</v>
       </c>
       <c r="G31">
         <v>12.8</v>
@@ -3829,28 +3829,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M31">
-        <v>8.053781399999998</v>
+        <v>8.331498</v>
       </c>
       <c r="N31">
-        <v>36.27955193333333</v>
+        <v>36.00183533333333</v>
       </c>
       <c r="O31">
-        <v>12.69784317666666</v>
+        <v>12.60064236666667</v>
       </c>
       <c r="P31">
-        <v>23.58170875666666</v>
+        <v>23.40119296666667</v>
       </c>
       <c r="Q31">
-        <v>62.58170875666666</v>
+        <v>62.40119296666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08261009525970781</v>
+        <v>0.08299051599138457</v>
       </c>
       <c r="T31">
-        <v>0.674189821853046</v>
+        <v>0.6811573611519486</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.504660622317529</v>
+        <v>5.321171934906944</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0688768611939692</v>
+        <v>0.06867650475354585</v>
       </c>
       <c r="C32">
-        <v>355.6794139392792</v>
+        <v>354.9799186772537</v>
       </c>
       <c r="D32">
-        <v>493.5394139392792</v>
+        <v>497.8619186772538</v>
       </c>
       <c r="E32">
-        <v>-74.64000000000001</v>
+        <v>-69.61800000000002</v>
       </c>
       <c r="F32">
-        <v>150.66</v>
+        <v>155.682</v>
       </c>
       <c r="G32">
         <v>12.8</v>
@@ -3911,28 +3911,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M32">
-        <v>8.331498</v>
+        <v>8.6092146</v>
       </c>
       <c r="N32">
-        <v>36.00183533333333</v>
+        <v>35.72411873333333</v>
       </c>
       <c r="O32">
-        <v>12.60064236666667</v>
+        <v>12.50344155666666</v>
       </c>
       <c r="P32">
-        <v>23.40119296666667</v>
+        <v>23.22067717666666</v>
       </c>
       <c r="Q32">
-        <v>62.40119296666667</v>
+        <v>62.22067717666666</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08299051599138457</v>
+        <v>0.08338196341093602</v>
       </c>
       <c r="T32">
-        <v>0.6811573611519486</v>
+        <v>0.688326858111689</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.321171934906944</v>
+        <v>5.1495212273293</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06867650475354585</v>
+        <v>0.0684761483131225</v>
       </c>
       <c r="C33">
-        <v>354.9799186772537</v>
+        <v>354.356806904263</v>
       </c>
       <c r="D33">
-        <v>497.8619186772538</v>
+        <v>502.2608069042631</v>
       </c>
       <c r="E33">
-        <v>-69.61800000000002</v>
+        <v>-64.596</v>
       </c>
       <c r="F33">
-        <v>155.682</v>
+        <v>160.704</v>
       </c>
       <c r="G33">
         <v>12.8</v>
@@ -3993,28 +3993,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M33">
-        <v>8.6092146</v>
+        <v>8.886931200000001</v>
       </c>
       <c r="N33">
-        <v>35.72411873333333</v>
+        <v>35.44640213333333</v>
       </c>
       <c r="O33">
-        <v>12.50344155666666</v>
+        <v>12.40624074666666</v>
       </c>
       <c r="P33">
-        <v>23.22067717666666</v>
+        <v>23.04016138666666</v>
       </c>
       <c r="Q33">
-        <v>62.22067717666666</v>
+        <v>62.04016138666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08338196341093602</v>
+        <v>0.08378492398988605</v>
       </c>
       <c r="T33">
-        <v>0.688326858111689</v>
+        <v>0.6957072226290688</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.1495212273293</v>
+        <v>4.988598688975259</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0684761483131225</v>
+        <v>0.06827579187269917</v>
       </c>
       <c r="C34">
-        <v>354.356806904263</v>
+        <v>353.8121213413008</v>
       </c>
       <c r="D34">
-        <v>502.2608069042631</v>
+        <v>506.7381213413008</v>
       </c>
       <c r="E34">
-        <v>-64.596</v>
+        <v>-59.57400000000001</v>
       </c>
       <c r="F34">
-        <v>160.704</v>
+        <v>165.726</v>
       </c>
       <c r="G34">
         <v>12.8</v>
@@ -4075,28 +4075,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M34">
-        <v>8.886931200000001</v>
+        <v>9.164647800000001</v>
       </c>
       <c r="N34">
-        <v>35.44640213333333</v>
+        <v>35.16868553333333</v>
       </c>
       <c r="O34">
-        <v>12.40624074666666</v>
+        <v>12.30903993666666</v>
       </c>
       <c r="P34">
-        <v>23.04016138666666</v>
+        <v>22.85964559666667</v>
       </c>
       <c r="Q34">
-        <v>62.04016138666667</v>
+        <v>61.85964559666667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08378492398988605</v>
+        <v>0.08419991324283459</v>
       </c>
       <c r="T34">
-        <v>0.6957072226290688</v>
+        <v>0.7033078965350271</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.988598688975259</v>
+        <v>4.837429031733585</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06827579187269917</v>
+        <v>0.06807543543227583</v>
       </c>
       <c r="C35">
-        <v>353.8121213413008</v>
+        <v>353.3479782023901</v>
       </c>
       <c r="D35">
-        <v>506.7381213413008</v>
+        <v>511.2959782023901</v>
       </c>
       <c r="E35">
-        <v>-59.57400000000001</v>
+        <v>-54.55199999999999</v>
       </c>
       <c r="F35">
-        <v>165.726</v>
+        <v>170.748</v>
       </c>
       <c r="G35">
         <v>12.8</v>
@@ -4157,28 +4157,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M35">
-        <v>9.164647800000001</v>
+        <v>9.442364400000001</v>
       </c>
       <c r="N35">
-        <v>35.16868553333333</v>
+        <v>34.89096893333333</v>
       </c>
       <c r="O35">
-        <v>12.30903993666666</v>
+        <v>12.21183912666666</v>
       </c>
       <c r="P35">
-        <v>22.85964559666667</v>
+        <v>22.67912980666666</v>
       </c>
       <c r="Q35">
-        <v>61.85964559666667</v>
+        <v>61.67912980666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08419991324283459</v>
+        <v>0.08462747792769065</v>
       </c>
       <c r="T35">
-        <v>0.7033078965350271</v>
+        <v>0.7111388938926811</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.837429031733585</v>
+        <v>4.695151707270831</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06807543543227583</v>
+        <v>0.06787507899185248</v>
       </c>
       <c r="C36">
-        <v>353.3479782023901</v>
+        <v>352.9665705297479</v>
       </c>
       <c r="D36">
-        <v>511.2959782023901</v>
+        <v>515.9365705297479</v>
       </c>
       <c r="E36">
-        <v>-54.55199999999999</v>
+        <v>-49.53</v>
       </c>
       <c r="F36">
-        <v>170.748</v>
+        <v>175.77</v>
       </c>
       <c r="G36">
         <v>12.8</v>
@@ -4239,28 +4239,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M36">
-        <v>9.442364400000001</v>
+        <v>9.720081</v>
       </c>
       <c r="N36">
-        <v>34.89096893333333</v>
+        <v>34.61325233333333</v>
       </c>
       <c r="O36">
-        <v>12.21183912666666</v>
+        <v>12.11463831666666</v>
       </c>
       <c r="P36">
-        <v>22.67912980666666</v>
+        <v>22.49861401666666</v>
       </c>
       <c r="Q36">
-        <v>61.67912980666667</v>
+        <v>61.49861401666666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08462747792769065</v>
+        <v>0.08506819844900382</v>
       </c>
       <c r="T36">
-        <v>0.7111388938926811</v>
+        <v>0.7192108450151861</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.695151707270831</v>
+        <v>4.561004515634522</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06787507899185248</v>
+        <v>0.06825972255142915</v>
       </c>
       <c r="C37">
-        <v>352.9665705297479</v>
+        <v>339.108678699387</v>
       </c>
       <c r="D37">
-        <v>515.9365705297479</v>
+        <v>507.1006786993871</v>
       </c>
       <c r="E37">
-        <v>-49.53</v>
+        <v>-44.50799999999998</v>
       </c>
       <c r="F37">
-        <v>175.77</v>
+        <v>180.792</v>
       </c>
       <c r="G37">
         <v>12.8</v>
@@ -4321,45 +4321,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M37">
-        <v>9.720081</v>
+        <v>10.4497776</v>
       </c>
       <c r="N37">
-        <v>34.61325233333333</v>
+        <v>33.88355573333332</v>
       </c>
       <c r="O37">
-        <v>12.11463831666666</v>
+        <v>11.85924450666666</v>
       </c>
       <c r="P37">
-        <v>22.49861401666666</v>
+        <v>22.02431122666666</v>
       </c>
       <c r="Q37">
-        <v>61.49861401666666</v>
+        <v>61.02431122666666</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08506819844900382</v>
+        <v>0.08552269148660804</v>
       </c>
       <c r="T37">
-        <v>0.7192108450151861</v>
+        <v>0.7275350446102692</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.35</v>
       </c>
       <c r="W37">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.561004515634522</v>
+        <v>4.242514532877074</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06825972255142915</v>
+        <v>0.06807561611100581</v>
       </c>
       <c r="C38">
-        <v>339.108678699387</v>
+        <v>338.2778310529905</v>
       </c>
       <c r="D38">
-        <v>507.1006786993871</v>
+        <v>511.2918310529904</v>
       </c>
       <c r="E38">
-        <v>-44.50800000000001</v>
+        <v>-39.48600000000002</v>
       </c>
       <c r="F38">
-        <v>180.792</v>
+        <v>185.814</v>
       </c>
       <c r="G38">
         <v>12.8</v>
@@ -4403,28 +4403,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M38">
-        <v>10.4497776</v>
+        <v>10.7400492</v>
       </c>
       <c r="N38">
-        <v>33.88355573333332</v>
+        <v>33.59328413333333</v>
       </c>
       <c r="O38">
-        <v>11.85924450666666</v>
+        <v>11.75764944666666</v>
       </c>
       <c r="P38">
-        <v>22.02431122666666</v>
+        <v>21.83563468666667</v>
       </c>
       <c r="Q38">
-        <v>61.02431122666666</v>
+        <v>60.83563468666667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08552269148660804</v>
+        <v>0.08599161287461238</v>
       </c>
       <c r="T38">
-        <v>0.7275350446102692</v>
+        <v>0.7361235045099581</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.242514532877075</v>
+        <v>4.127851977934451</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06807561611100581</v>
+        <v>0.06789150967058245</v>
       </c>
       <c r="C39">
-        <v>338.2778310529905</v>
+        <v>337.5168399399499</v>
       </c>
       <c r="D39">
-        <v>511.2918310529904</v>
+        <v>515.55283993995</v>
       </c>
       <c r="E39">
-        <v>-39.48600000000002</v>
+        <v>-34.46400000000003</v>
       </c>
       <c r="F39">
-        <v>185.814</v>
+        <v>190.836</v>
       </c>
       <c r="G39">
         <v>12.8</v>
@@ -4485,28 +4485,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M39">
-        <v>10.7400492</v>
+        <v>11.0303208</v>
       </c>
       <c r="N39">
-        <v>33.59328413333333</v>
+        <v>33.30301253333333</v>
       </c>
       <c r="O39">
-        <v>11.75764944666666</v>
+        <v>11.65605438666666</v>
       </c>
       <c r="P39">
-        <v>21.83563468666667</v>
+        <v>21.64695814666667</v>
       </c>
       <c r="Q39">
-        <v>60.83563468666667</v>
+        <v>60.64695814666666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08599161287461238</v>
+        <v>0.08647566075900395</v>
       </c>
       <c r="T39">
-        <v>0.7361235045099581</v>
+        <v>0.7449890115031855</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.127851977934451</v>
+        <v>4.019224294304598</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06789150967058245</v>
+        <v>0.06859465323015912</v>
       </c>
       <c r="C40">
-        <v>337.5168399399499</v>
+        <v>316.5916517946875</v>
       </c>
       <c r="D40">
-        <v>515.55283993995</v>
+        <v>499.6496517946875</v>
       </c>
       <c r="E40">
-        <v>-34.46400000000003</v>
+        <v>-29.44200000000001</v>
       </c>
       <c r="F40">
-        <v>190.836</v>
+        <v>195.858</v>
       </c>
       <c r="G40">
         <v>12.8</v>
@@ -4567,45 +4567,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M40">
-        <v>11.0303208</v>
+        <v>12.0060954</v>
       </c>
       <c r="N40">
-        <v>33.30301253333333</v>
+        <v>32.32723793333333</v>
       </c>
       <c r="O40">
-        <v>11.65605438666666</v>
+        <v>11.31453327666666</v>
       </c>
       <c r="P40">
-        <v>21.64695814666667</v>
+        <v>21.01270465666666</v>
       </c>
       <c r="Q40">
-        <v>60.64695814666666</v>
+        <v>60.01270465666666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08647566075900395</v>
+        <v>0.08697557906583461</v>
       </c>
       <c r="T40">
-        <v>0.7449890115031855</v>
+        <v>0.7541451908568466</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.35</v>
       </c>
       <c r="W40">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.019224294304598</v>
+        <v>3.692568804120391</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06859465323015912</v>
+        <v>0.06843329678973577</v>
       </c>
       <c r="C41">
-        <v>316.5916517946875</v>
+        <v>315.1317351279878</v>
       </c>
       <c r="D41">
-        <v>499.6496517946875</v>
+        <v>503.2117351279878</v>
       </c>
       <c r="E41">
-        <v>-29.44200000000001</v>
+        <v>-24.42000000000002</v>
       </c>
       <c r="F41">
-        <v>195.858</v>
+        <v>200.88</v>
       </c>
       <c r="G41">
         <v>12.8</v>
@@ -4649,28 +4649,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M41">
-        <v>12.0060954</v>
+        <v>12.313944</v>
       </c>
       <c r="N41">
-        <v>32.32723793333333</v>
+        <v>32.01938933333333</v>
       </c>
       <c r="O41">
-        <v>11.31453327666666</v>
+        <v>11.20678626666666</v>
       </c>
       <c r="P41">
-        <v>21.01270465666666</v>
+        <v>20.81260306666666</v>
       </c>
       <c r="Q41">
-        <v>60.01270465666666</v>
+        <v>59.81260306666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08697557906583461</v>
+        <v>0.08749216131622628</v>
       </c>
       <c r="T41">
-        <v>0.7541451908568466</v>
+        <v>0.7636065761889629</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.692568804120391</v>
+        <v>3.600254584017382</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06843329678973577</v>
+        <v>0.06827194034931242</v>
       </c>
       <c r="C42">
-        <v>315.1317351279878</v>
+        <v>313.7229724852148</v>
       </c>
       <c r="D42">
-        <v>503.2117351279878</v>
+        <v>506.8249724852148</v>
       </c>
       <c r="E42">
-        <v>-24.42000000000002</v>
+        <v>-19.398</v>
       </c>
       <c r="F42">
-        <v>200.88</v>
+        <v>205.902</v>
       </c>
       <c r="G42">
         <v>12.8</v>
@@ -4731,28 +4731,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M42">
-        <v>12.313944</v>
+        <v>12.6217926</v>
       </c>
       <c r="N42">
-        <v>32.01938933333333</v>
+        <v>31.71154073333333</v>
       </c>
       <c r="O42">
-        <v>11.20678626666666</v>
+        <v>11.09903925666666</v>
       </c>
       <c r="P42">
-        <v>20.81260306666666</v>
+        <v>20.61250147666667</v>
       </c>
       <c r="Q42">
-        <v>59.81260306666667</v>
+        <v>59.61250147666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08749216131622628</v>
+        <v>0.08802625482934309</v>
       </c>
       <c r="T42">
-        <v>0.7636065761889629</v>
+        <v>0.7733886864475917</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.600254584017382</v>
+        <v>3.512443496602323</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06827194034931242</v>
+        <v>0.06887498390888909</v>
       </c>
       <c r="C43">
-        <v>313.7229724852148</v>
+        <v>295.4555662610269</v>
       </c>
       <c r="D43">
-        <v>506.8249724852148</v>
+        <v>493.5795662610269</v>
       </c>
       <c r="E43">
-        <v>-19.398</v>
+        <v>-14.376</v>
       </c>
       <c r="F43">
-        <v>205.902</v>
+        <v>210.924</v>
       </c>
       <c r="G43">
         <v>12.8</v>
@@ -4813,45 +4813,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M43">
-        <v>12.6217926</v>
+        <v>13.5202284</v>
       </c>
       <c r="N43">
-        <v>31.71154073333333</v>
+        <v>30.81310493333333</v>
       </c>
       <c r="O43">
-        <v>11.09903925666666</v>
+        <v>10.78458672666666</v>
       </c>
       <c r="P43">
-        <v>20.61250147666667</v>
+        <v>20.02851820666666</v>
       </c>
       <c r="Q43">
-        <v>59.61250147666667</v>
+        <v>59.02851820666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08802625482934309</v>
+        <v>0.08857876536015359</v>
       </c>
       <c r="T43">
-        <v>0.7733886864475917</v>
+        <v>0.7835081108530698</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.35</v>
       </c>
       <c r="W43">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.512443496602323</v>
+        <v>3.279037307781969</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06887498390888909</v>
+        <v>0.06873182746846575</v>
       </c>
       <c r="C44">
-        <v>295.4555662610269</v>
+        <v>293.5148337207961</v>
       </c>
       <c r="D44">
-        <v>493.5795662610269</v>
+        <v>496.6608337207961</v>
       </c>
       <c r="E44">
-        <v>-14.37600000000003</v>
+        <v>-9.354000000000013</v>
       </c>
       <c r="F44">
-        <v>210.924</v>
+        <v>215.946</v>
       </c>
       <c r="G44">
         <v>12.8</v>
@@ -4895,28 +4895,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M44">
-        <v>13.5202284</v>
+        <v>13.8421386</v>
       </c>
       <c r="N44">
-        <v>30.81310493333333</v>
+        <v>30.49119473333333</v>
       </c>
       <c r="O44">
-        <v>10.78458672666666</v>
+        <v>10.67191815666667</v>
       </c>
       <c r="P44">
-        <v>20.02851820666666</v>
+        <v>19.81927657666667</v>
       </c>
       <c r="Q44">
-        <v>59.02851820666666</v>
+        <v>58.81927657666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08857876536015359</v>
+        <v>0.08915066222537849</v>
       </c>
       <c r="T44">
-        <v>0.7835081108530698</v>
+        <v>0.7939826027815472</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.27903730778197</v>
+        <v>3.202780626205645</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06873182746846575</v>
+        <v>0.06858867102804241</v>
       </c>
       <c r="C45">
-        <v>293.5148337207961</v>
+        <v>291.6128136865285</v>
       </c>
       <c r="D45">
-        <v>496.6608337207961</v>
+        <v>499.7808136865285</v>
       </c>
       <c r="E45">
-        <v>-9.354000000000013</v>
+        <v>-4.332000000000022</v>
       </c>
       <c r="F45">
-        <v>215.946</v>
+        <v>220.968</v>
       </c>
       <c r="G45">
         <v>12.8</v>
@@ -4977,28 +4977,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M45">
-        <v>13.8421386</v>
+        <v>14.1640488</v>
       </c>
       <c r="N45">
-        <v>30.49119473333333</v>
+        <v>30.16928453333333</v>
       </c>
       <c r="O45">
-        <v>10.67191815666667</v>
+        <v>10.55924958666666</v>
       </c>
       <c r="P45">
-        <v>19.81927657666667</v>
+        <v>19.61003494666667</v>
       </c>
       <c r="Q45">
-        <v>58.81927657666667</v>
+        <v>58.61003494666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08915066222537849</v>
+        <v>0.08974298397864713</v>
       </c>
       <c r="T45">
-        <v>0.7939826027815472</v>
+        <v>0.80483118370747</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.202780626205645</v>
+        <v>3.129990157428244</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06858867102804241</v>
+        <v>0.06844551458761906</v>
       </c>
       <c r="C46">
-        <v>291.6128136865285</v>
+        <v>289.7502403360056</v>
       </c>
       <c r="D46">
-        <v>499.7808136865285</v>
+        <v>502.9402403360056</v>
       </c>
       <c r="E46">
-        <v>-4.332000000000022</v>
+        <v>0.6899999999999977</v>
       </c>
       <c r="F46">
-        <v>220.968</v>
+        <v>225.99</v>
       </c>
       <c r="G46">
         <v>12.8</v>
@@ -5059,28 +5059,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M46">
-        <v>14.1640488</v>
+        <v>14.485959</v>
       </c>
       <c r="N46">
-        <v>30.16928453333333</v>
+        <v>29.84737433333333</v>
       </c>
       <c r="O46">
-        <v>10.55924958666666</v>
+        <v>10.44658101666666</v>
       </c>
       <c r="P46">
-        <v>19.61003494666667</v>
+        <v>19.40079331666666</v>
       </c>
       <c r="Q46">
-        <v>58.61003494666667</v>
+        <v>58.40079331666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08974298397864713</v>
+        <v>0.09035684470476191</v>
       </c>
       <c r="T46">
-        <v>0.80483118370747</v>
+        <v>0.8160742584852446</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.129990157428244</v>
+        <v>3.060434820596505</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06844551458761906</v>
+        <v>0.07063455814719571</v>
       </c>
       <c r="C47">
-        <v>289.7502403360056</v>
+        <v>240.3965438574924</v>
       </c>
       <c r="D47">
-        <v>502.9402403360056</v>
+        <v>458.6085438574924</v>
       </c>
       <c r="E47">
-        <v>0.6899999999999977</v>
+        <v>5.711999999999989</v>
       </c>
       <c r="F47">
-        <v>225.99</v>
+        <v>231.012</v>
       </c>
       <c r="G47">
         <v>12.8</v>
@@ -5141,45 +5141,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M47">
-        <v>14.485959</v>
+        <v>16.6097628</v>
       </c>
       <c r="N47">
-        <v>29.84737433333333</v>
+        <v>27.72357053333333</v>
       </c>
       <c r="O47">
-        <v>10.44658101666666</v>
+        <v>9.703249686666664</v>
       </c>
       <c r="P47">
-        <v>19.40079331666666</v>
+        <v>18.02032084666666</v>
       </c>
       <c r="Q47">
-        <v>58.40079331666666</v>
+        <v>57.02032084666666</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09035684470476191</v>
+        <v>0.09099344101332539</v>
       </c>
       <c r="T47">
-        <v>0.8160742584852446</v>
+        <v>0.8277337434399741</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.35</v>
       </c>
       <c r="W47">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.060434820596505</v>
+        <v>2.669112970916919</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07063455814719571</v>
+        <v>0.07054210170677237</v>
       </c>
       <c r="C48">
-        <v>240.3965438574924</v>
+        <v>237.0882751328428</v>
       </c>
       <c r="D48">
-        <v>458.6085438574924</v>
+        <v>460.3222751328428</v>
       </c>
       <c r="E48">
-        <v>5.711999999999989</v>
+        <v>10.73400000000001</v>
       </c>
       <c r="F48">
-        <v>231.012</v>
+        <v>236.034</v>
       </c>
       <c r="G48">
         <v>12.8</v>
@@ -5223,28 +5223,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M48">
-        <v>16.6097628</v>
+        <v>16.9708446</v>
       </c>
       <c r="N48">
-        <v>27.72357053333333</v>
+        <v>27.36248873333333</v>
       </c>
       <c r="O48">
-        <v>9.703249686666664</v>
+        <v>9.576871056666663</v>
       </c>
       <c r="P48">
-        <v>18.02032084666666</v>
+        <v>17.78561767666666</v>
       </c>
       <c r="Q48">
-        <v>57.02032084666666</v>
+        <v>56.78561767666666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09099344101332539</v>
+        <v>0.0916540598240988</v>
       </c>
       <c r="T48">
-        <v>0.8277337434399741</v>
+        <v>0.8398332089590327</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.669112970916919</v>
+        <v>2.612323333237835</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07054210170677237</v>
+        <v>0.07044964526634903</v>
       </c>
       <c r="C49">
-        <v>237.0882751328428</v>
+        <v>233.7928622113376</v>
       </c>
       <c r="D49">
-        <v>460.3222751328428</v>
+        <v>462.0488622113376</v>
       </c>
       <c r="E49">
-        <v>10.73400000000001</v>
+        <v>15.756</v>
       </c>
       <c r="F49">
-        <v>236.034</v>
+        <v>241.056</v>
       </c>
       <c r="G49">
         <v>12.8</v>
@@ -5305,28 +5305,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M49">
-        <v>16.9708446</v>
+        <v>17.3319264</v>
       </c>
       <c r="N49">
-        <v>27.36248873333333</v>
+        <v>27.00140693333332</v>
       </c>
       <c r="O49">
-        <v>9.576871056666663</v>
+        <v>9.450492426666663</v>
       </c>
       <c r="P49">
-        <v>17.78561767666666</v>
+        <v>17.55091450666666</v>
       </c>
       <c r="Q49">
-        <v>56.78561767666666</v>
+        <v>56.55091450666666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.0916540598240988</v>
+        <v>0.0923400870506712</v>
       </c>
       <c r="T49">
-        <v>0.8398332089590327</v>
+        <v>0.8523980385365167</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.612323333237835</v>
+        <v>2.557899930462047</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07044964526634903</v>
+        <v>0.07035718882592568</v>
       </c>
       <c r="C50">
-        <v>233.7928622113376</v>
+        <v>230.5104502971131</v>
       </c>
       <c r="D50">
-        <v>462.0488622113376</v>
+        <v>463.7884502971131</v>
       </c>
       <c r="E50">
-        <v>15.75599999999997</v>
+        <v>20.77799999999999</v>
       </c>
       <c r="F50">
-        <v>241.056</v>
+        <v>246.078</v>
       </c>
       <c r="G50">
         <v>12.8</v>
@@ -5387,28 +5387,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M50">
-        <v>17.3319264</v>
+        <v>17.6930082</v>
       </c>
       <c r="N50">
-        <v>27.00140693333333</v>
+        <v>26.64032513333333</v>
       </c>
       <c r="O50">
-        <v>9.450492426666663</v>
+        <v>9.324113796666664</v>
       </c>
       <c r="P50">
-        <v>17.55091450666666</v>
+        <v>17.31621133666666</v>
       </c>
       <c r="Q50">
-        <v>56.55091450666666</v>
+        <v>56.31621133666666</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0923400870506712</v>
+        <v>0.09305301730573662</v>
       </c>
       <c r="T50">
-        <v>0.8523980385365167</v>
+        <v>0.865455606528804</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.557899930462048</v>
+        <v>2.505697891064863</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07035718882592568</v>
+        <v>0.07153223238550234</v>
       </c>
       <c r="C51">
-        <v>230.5104502971131</v>
+        <v>204.3098901409914</v>
       </c>
       <c r="D51">
-        <v>463.7884502971131</v>
+        <v>442.6098901409914</v>
       </c>
       <c r="E51">
-        <v>20.77799999999999</v>
+        <v>25.79999999999998</v>
       </c>
       <c r="F51">
-        <v>246.078</v>
+        <v>251.1</v>
       </c>
       <c r="G51">
         <v>12.8</v>
@@ -5469,45 +5469,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M51">
-        <v>17.6930082</v>
+        <v>19.03338</v>
       </c>
       <c r="N51">
-        <v>26.64032513333333</v>
+        <v>25.29995333333333</v>
       </c>
       <c r="O51">
-        <v>9.324113796666664</v>
+        <v>8.854983666666664</v>
       </c>
       <c r="P51">
-        <v>17.31621133666666</v>
+        <v>16.44496966666667</v>
       </c>
       <c r="Q51">
-        <v>56.31621133666666</v>
+        <v>55.44496966666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09305301730573662</v>
+        <v>0.09379446477100467</v>
       </c>
       <c r="T51">
-        <v>0.865455606528804</v>
+        <v>0.8790354772407828</v>
       </c>
       <c r="U51">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.35</v>
       </c>
       <c r="W51">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.505697891064863</v>
+        <v>2.329241224277208</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07153223238550234</v>
+        <v>0.07146512594507901</v>
       </c>
       <c r="C52">
-        <v>204.3098901409914</v>
+        <v>200.4451793858245</v>
       </c>
       <c r="D52">
-        <v>442.6098901409914</v>
+        <v>443.7671793858245</v>
       </c>
       <c r="E52">
-        <v>25.79999999999998</v>
+        <v>30.822</v>
       </c>
       <c r="F52">
-        <v>251.1</v>
+        <v>256.122</v>
       </c>
       <c r="G52">
         <v>12.8</v>
@@ -5551,28 +5551,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M52">
-        <v>19.03338</v>
+        <v>19.4140476</v>
       </c>
       <c r="N52">
-        <v>25.29995333333333</v>
+        <v>24.91928573333333</v>
       </c>
       <c r="O52">
-        <v>8.854983666666664</v>
+        <v>8.721750006666664</v>
       </c>
       <c r="P52">
-        <v>16.44496966666667</v>
+        <v>16.19753572666666</v>
       </c>
       <c r="Q52">
-        <v>55.44496966666667</v>
+        <v>55.19753572666666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09379446477100467</v>
+        <v>0.0945661753981204</v>
       </c>
       <c r="T52">
-        <v>0.8790354772407828</v>
+        <v>0.8931696283899854</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.329241224277208</v>
+        <v>2.283569827722753</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07146512594507901</v>
+        <v>0.07139801950465566</v>
       </c>
       <c r="C53">
-        <v>200.4451793858245</v>
+        <v>196.5865364095925</v>
       </c>
       <c r="D53">
-        <v>443.7671793858245</v>
+        <v>444.9305364095925</v>
       </c>
       <c r="E53">
-        <v>30.822</v>
+        <v>35.84399999999999</v>
       </c>
       <c r="F53">
-        <v>256.122</v>
+        <v>261.144</v>
       </c>
       <c r="G53">
         <v>12.8</v>
@@ -5633,28 +5633,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M53">
-        <v>19.4140476</v>
+        <v>19.7947152</v>
       </c>
       <c r="N53">
-        <v>24.91928573333333</v>
+        <v>24.53861813333333</v>
       </c>
       <c r="O53">
-        <v>8.721750006666664</v>
+        <v>8.588516346666664</v>
       </c>
       <c r="P53">
-        <v>16.19753572666666</v>
+        <v>15.95010178666666</v>
       </c>
       <c r="Q53">
-        <v>55.19753572666666</v>
+        <v>54.95010178666666</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0945661753981204</v>
+        <v>0.09537004063469928</v>
       </c>
       <c r="T53">
-        <v>0.8931696283899854</v>
+        <v>0.907892702503738</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.283569827722753</v>
+        <v>2.239655023343469</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07139801950465566</v>
+        <v>0.07133091306423231</v>
       </c>
       <c r="C54">
-        <v>196.5865364095925</v>
+        <v>192.7340090586505</v>
       </c>
       <c r="D54">
-        <v>444.9305364095925</v>
+        <v>446.1000090586505</v>
       </c>
       <c r="E54">
-        <v>35.84399999999999</v>
+        <v>40.86599999999999</v>
       </c>
       <c r="F54">
-        <v>261.144</v>
+        <v>266.166</v>
       </c>
       <c r="G54">
         <v>12.8</v>
@@ -5715,28 +5715,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M54">
-        <v>19.7947152</v>
+        <v>20.1753828</v>
       </c>
       <c r="N54">
-        <v>24.53861813333333</v>
+        <v>24.15795053333333</v>
       </c>
       <c r="O54">
-        <v>8.588516346666664</v>
+        <v>8.455282686666663</v>
       </c>
       <c r="P54">
-        <v>15.95010178666666</v>
+        <v>15.70266784666666</v>
       </c>
       <c r="Q54">
-        <v>54.95010178666666</v>
+        <v>54.70266784666666</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09537004063469928</v>
+        <v>0.09620811290262193</v>
       </c>
       <c r="T54">
-        <v>0.907892702503738</v>
+        <v>0.9232422904095651</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.239655023343469</v>
+        <v>2.197397381393593</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07133091306423231</v>
+        <v>0.07126380662380896</v>
       </c>
       <c r="C55">
-        <v>192.7340090586505</v>
+        <v>188.8876456837244</v>
       </c>
       <c r="D55">
-        <v>446.1000090586505</v>
+        <v>447.2756456837244</v>
       </c>
       <c r="E55">
-        <v>40.86599999999999</v>
+        <v>45.88799999999998</v>
       </c>
       <c r="F55">
-        <v>266.166</v>
+        <v>271.188</v>
       </c>
       <c r="G55">
         <v>12.8</v>
@@ -5797,28 +5797,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M55">
-        <v>20.1753828</v>
+        <v>20.5560504</v>
       </c>
       <c r="N55">
-        <v>24.15795053333333</v>
+        <v>23.77728293333333</v>
       </c>
       <c r="O55">
-        <v>8.455282686666663</v>
+        <v>8.322049026666665</v>
       </c>
       <c r="P55">
-        <v>15.70266784666666</v>
+        <v>15.45523390666666</v>
       </c>
       <c r="Q55">
-        <v>54.70266784666666</v>
+        <v>54.45523390666666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09620811290262193</v>
+        <v>0.09708262309523688</v>
       </c>
       <c r="T55">
-        <v>0.9232422904095651</v>
+        <v>0.939259251702602</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.197397381393593</v>
+        <v>2.156704837293711</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07126380662380896</v>
+        <v>0.07119670018338563</v>
       </c>
       <c r="C56">
-        <v>188.8876456837244</v>
+        <v>185.0474951465739</v>
       </c>
       <c r="D56">
-        <v>447.2756456837244</v>
+        <v>448.4574951465739</v>
       </c>
       <c r="E56">
-        <v>45.88799999999998</v>
+        <v>50.91000000000003</v>
       </c>
       <c r="F56">
-        <v>271.188</v>
+        <v>276.21</v>
       </c>
       <c r="G56">
         <v>12.8</v>
@@ -5879,28 +5879,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M56">
-        <v>20.5560504</v>
+        <v>20.93671800000001</v>
       </c>
       <c r="N56">
-        <v>23.77728293333333</v>
+        <v>23.39661533333332</v>
       </c>
       <c r="O56">
-        <v>8.322049026666665</v>
+        <v>8.188815366666663</v>
       </c>
       <c r="P56">
-        <v>15.45523390666666</v>
+        <v>15.20779996666666</v>
       </c>
       <c r="Q56">
-        <v>54.45523390666666</v>
+        <v>54.20779996666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09708262309523688</v>
+        <v>0.09799600040752361</v>
       </c>
       <c r="T56">
-        <v>0.939259251702602</v>
+        <v>0.9559880779419964</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.156704837293711</v>
+        <v>2.117492022070189</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07119670018338563</v>
+        <v>0.07112959374296228</v>
       </c>
       <c r="C57">
-        <v>185.0474951465739</v>
+        <v>181.2136068267629</v>
       </c>
       <c r="D57">
-        <v>448.4574951465739</v>
+        <v>449.645606826763</v>
       </c>
       <c r="E57">
-        <v>50.91000000000003</v>
+        <v>55.93200000000002</v>
       </c>
       <c r="F57">
-        <v>276.21</v>
+        <v>281.232</v>
       </c>
       <c r="G57">
         <v>12.8</v>
@@ -5961,28 +5961,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M57">
-        <v>20.93671800000001</v>
+        <v>21.31738560000001</v>
       </c>
       <c r="N57">
-        <v>23.39661533333332</v>
+        <v>23.01594773333332</v>
       </c>
       <c r="O57">
-        <v>8.188815366666663</v>
+        <v>8.055581706666663</v>
       </c>
       <c r="P57">
-        <v>15.20779996666666</v>
+        <v>14.96036602666666</v>
       </c>
       <c r="Q57">
-        <v>54.20779996666666</v>
+        <v>53.96036602666666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09799600040752361</v>
+        <v>0.09895089487036882</v>
       </c>
       <c r="T57">
-        <v>0.9559880779419964</v>
+        <v>0.9734773053740902</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.117492022070189</v>
+        <v>2.079679664533221</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07112959374296228</v>
+        <v>0.07106248730253895</v>
       </c>
       <c r="C58">
-        <v>181.2136068267629</v>
+        <v>177.3860306285357</v>
       </c>
       <c r="D58">
-        <v>449.645606826763</v>
+        <v>450.8400306285357</v>
       </c>
       <c r="E58">
-        <v>55.93200000000002</v>
+        <v>60.95400000000001</v>
       </c>
       <c r="F58">
-        <v>281.232</v>
+        <v>286.254</v>
       </c>
       <c r="G58">
         <v>12.8</v>
@@ -6043,28 +6043,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M58">
-        <v>21.31738560000001</v>
+        <v>21.6980532</v>
       </c>
       <c r="N58">
-        <v>23.01594773333332</v>
+        <v>22.63528013333332</v>
       </c>
       <c r="O58">
-        <v>8.055581706666663</v>
+        <v>7.922348046666663</v>
       </c>
       <c r="P58">
-        <v>14.96036602666666</v>
+        <v>14.71293208666666</v>
       </c>
       <c r="Q58">
-        <v>53.96036602666666</v>
+        <v>53.71293208666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09895089487036882</v>
+        <v>0.09995020302916031</v>
       </c>
       <c r="T58">
-        <v>0.9734773053740902</v>
+        <v>0.9917799852448862</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.079679664533221</v>
+        <v>2.043194056383515</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07106248730253895</v>
+        <v>0.0709953808621156</v>
       </c>
       <c r="C59">
-        <v>177.3860306285357</v>
+        <v>173.5648169878054</v>
       </c>
       <c r="D59">
-        <v>450.8400306285357</v>
+        <v>452.0408169878054</v>
       </c>
       <c r="E59">
-        <v>60.95400000000001</v>
+        <v>65.976</v>
       </c>
       <c r="F59">
-        <v>286.254</v>
+        <v>291.276</v>
       </c>
       <c r="G59">
         <v>12.8</v>
@@ -6125,28 +6125,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M59">
-        <v>21.6980532</v>
+        <v>22.0787208</v>
       </c>
       <c r="N59">
-        <v>22.63528013333332</v>
+        <v>22.25461253333333</v>
       </c>
       <c r="O59">
-        <v>7.922348046666663</v>
+        <v>7.789114386666664</v>
       </c>
       <c r="P59">
-        <v>14.71293208666666</v>
+        <v>14.46549814666666</v>
       </c>
       <c r="Q59">
-        <v>53.71293208666666</v>
+        <v>53.46549814666666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09995020302916031</v>
+        <v>0.1009970972907514</v>
       </c>
       <c r="T59">
-        <v>0.9917799852448862</v>
+        <v>1.010954221300006</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.043194056383515</v>
+        <v>2.007966572652765</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0709953808621156</v>
+        <v>0.07637397442169225</v>
       </c>
       <c r="C60">
-        <v>173.5648169878055</v>
+        <v>89.01950106616528</v>
       </c>
       <c r="D60">
-        <v>452.0408169878054</v>
+        <v>372.5175010661653</v>
       </c>
       <c r="E60">
-        <v>65.97599999999994</v>
+        <v>70.99799999999999</v>
       </c>
       <c r="F60">
-        <v>291.276</v>
+        <v>296.298</v>
       </c>
       <c r="G60">
         <v>12.8</v>
@@ -6207,45 +6207,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M60">
-        <v>22.0787208</v>
+        <v>26.66682</v>
       </c>
       <c r="N60">
-        <v>22.25461253333333</v>
+        <v>17.66651333333333</v>
       </c>
       <c r="O60">
-        <v>7.789114386666665</v>
+        <v>6.183279666666666</v>
       </c>
       <c r="P60">
-        <v>14.46549814666666</v>
+        <v>11.48323366666667</v>
       </c>
       <c r="Q60">
-        <v>53.46549814666666</v>
+        <v>50.48323366666666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1009970972907514</v>
+        <v>0.102095059565103</v>
       </c>
       <c r="T60">
-        <v>1.010954221300006</v>
+        <v>1.03106378594318</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0.35</v>
       </c>
       <c r="W60">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.007966572652766</v>
+        <v>1.662490440679966</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07637397442169225</v>
+        <v>0.0763991679812689</v>
       </c>
       <c r="C61">
-        <v>89.01950106616528</v>
+        <v>83.6907920124354</v>
       </c>
       <c r="D61">
-        <v>372.5175010661653</v>
+        <v>372.2107920124354</v>
       </c>
       <c r="E61">
-        <v>70.99799999999999</v>
+        <v>76.01999999999998</v>
       </c>
       <c r="F61">
-        <v>296.298</v>
+        <v>301.32</v>
       </c>
       <c r="G61">
         <v>12.8</v>
@@ -6289,28 +6289,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M61">
-        <v>26.66682</v>
+        <v>27.1188</v>
       </c>
       <c r="N61">
-        <v>17.66651333333333</v>
+        <v>17.21453333333333</v>
       </c>
       <c r="O61">
-        <v>6.183279666666666</v>
+        <v>6.025086666666666</v>
       </c>
       <c r="P61">
-        <v>11.48323366666667</v>
+        <v>11.18944666666667</v>
       </c>
       <c r="Q61">
-        <v>50.48323366666666</v>
+        <v>50.18944666666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.102095059565103</v>
+        <v>0.1032479199531723</v>
       </c>
       <c r="T61">
-        <v>1.03106378594318</v>
+        <v>1.052178828818513</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.662490440679966</v>
+        <v>1.634782266668633</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0763991679812689</v>
+        <v>0.07642436154084556</v>
       </c>
       <c r="C62">
-        <v>83.6907920124354</v>
+        <v>78.36258759569569</v>
       </c>
       <c r="D62">
-        <v>372.2107920124354</v>
+        <v>371.9045875956957</v>
       </c>
       <c r="E62">
-        <v>76.01999999999998</v>
+        <v>81.04199999999997</v>
       </c>
       <c r="F62">
-        <v>301.32</v>
+        <v>306.342</v>
       </c>
       <c r="G62">
         <v>12.8</v>
@@ -6371,28 +6371,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M62">
-        <v>27.1188</v>
+        <v>27.57078</v>
       </c>
       <c r="N62">
-        <v>17.21453333333333</v>
+        <v>16.76255333333333</v>
       </c>
       <c r="O62">
-        <v>6.025086666666666</v>
+        <v>5.866893666666665</v>
       </c>
       <c r="P62">
-        <v>11.18944666666667</v>
+        <v>10.89565966666666</v>
       </c>
       <c r="Q62">
-        <v>50.18944666666667</v>
+        <v>49.89565966666666</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1032479199531723</v>
+        <v>0.1044599013867835</v>
       </c>
       <c r="T62">
-        <v>1.052178828818513</v>
+        <v>1.074376694405401</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.634782266668633</v>
+        <v>1.607982557378983</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07642436154084556</v>
+        <v>0.07644955510042223</v>
       </c>
       <c r="C63">
-        <v>78.36258759569569</v>
+        <v>73.03488657152985</v>
       </c>
       <c r="D63">
-        <v>371.9045875956957</v>
+        <v>371.5988865715298</v>
       </c>
       <c r="E63">
-        <v>81.04199999999997</v>
+        <v>86.06399999999996</v>
       </c>
       <c r="F63">
-        <v>306.342</v>
+        <v>311.364</v>
       </c>
       <c r="G63">
         <v>12.8</v>
@@ -6453,28 +6453,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M63">
-        <v>27.57078</v>
+        <v>28.02276</v>
       </c>
       <c r="N63">
-        <v>16.76255333333333</v>
+        <v>16.31057333333333</v>
       </c>
       <c r="O63">
-        <v>5.866893666666665</v>
+        <v>5.708700666666665</v>
       </c>
       <c r="P63">
-        <v>10.89565966666666</v>
+        <v>10.60187266666667</v>
       </c>
       <c r="Q63">
-        <v>49.89565966666666</v>
+        <v>49.60187266666667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1044599013867835</v>
+        <v>0.1057356713169006</v>
       </c>
       <c r="T63">
-        <v>1.074376694405401</v>
+        <v>1.097742868707389</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.607982557378983</v>
+        <v>1.582047354840613</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07644955510042223</v>
+        <v>0.07647474865999887</v>
       </c>
       <c r="C64">
-        <v>73.03488657152985</v>
+        <v>67.70768769961006</v>
       </c>
       <c r="D64">
-        <v>371.5988865715298</v>
+        <v>371.29368769961</v>
       </c>
       <c r="E64">
-        <v>86.06399999999996</v>
+        <v>91.08599999999996</v>
       </c>
       <c r="F64">
-        <v>311.364</v>
+        <v>316.386</v>
       </c>
       <c r="G64">
         <v>12.8</v>
@@ -6535,28 +6535,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M64">
-        <v>28.02276</v>
+        <v>28.47474</v>
       </c>
       <c r="N64">
-        <v>16.31057333333333</v>
+        <v>15.85859333333333</v>
       </c>
       <c r="O64">
-        <v>5.708700666666665</v>
+        <v>5.550507666666666</v>
       </c>
       <c r="P64">
-        <v>10.60187266666667</v>
+        <v>10.30808566666667</v>
       </c>
       <c r="Q64">
-        <v>49.60187266666667</v>
+        <v>49.30808566666667</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1057356713169006</v>
+        <v>0.1070804017837807</v>
       </c>
       <c r="T64">
-        <v>1.097742868707389</v>
+        <v>1.122372079458133</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.582047354840613</v>
+        <v>1.556935492065365</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07647474865999887</v>
+        <v>0.07649994221957554</v>
       </c>
       <c r="C65">
-        <v>67.70768769961006</v>
+        <v>62.38098974367915</v>
       </c>
       <c r="D65">
-        <v>371.29368769961</v>
+        <v>370.9889897436792</v>
       </c>
       <c r="E65">
-        <v>91.08599999999996</v>
+        <v>96.108</v>
       </c>
       <c r="F65">
-        <v>316.386</v>
+        <v>321.408</v>
       </c>
       <c r="G65">
         <v>12.8</v>
@@ -6617,28 +6617,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M65">
-        <v>28.47474</v>
+        <v>28.92672</v>
       </c>
       <c r="N65">
-        <v>15.85859333333333</v>
+        <v>15.40661333333333</v>
       </c>
       <c r="O65">
-        <v>5.550507666666666</v>
+        <v>5.392314666666665</v>
       </c>
       <c r="P65">
-        <v>10.30808566666667</v>
+        <v>10.01429866666667</v>
       </c>
       <c r="Q65">
-        <v>49.30808566666667</v>
+        <v>49.01429866666666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1070804017837807</v>
+        <v>0.1084998394988209</v>
       </c>
       <c r="T65">
-        <v>1.122372079458133</v>
+        <v>1.14836957969503</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.556935492065365</v>
+        <v>1.532608375001844</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07649994221957554</v>
+        <v>0.07652513577915218</v>
       </c>
       <c r="C66">
-        <v>62.38098974367915</v>
+        <v>57.05479147153585</v>
       </c>
       <c r="D66">
-        <v>370.9889897436792</v>
+        <v>370.6847914715358</v>
       </c>
       <c r="E66">
-        <v>96.108</v>
+        <v>101.13</v>
       </c>
       <c r="F66">
-        <v>321.408</v>
+        <v>326.43</v>
       </c>
       <c r="G66">
         <v>12.8</v>
@@ -6699,28 +6699,28 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M66">
-        <v>28.92672</v>
+        <v>29.3787</v>
       </c>
       <c r="N66">
-        <v>15.40661333333333</v>
+        <v>14.95463333333333</v>
       </c>
       <c r="O66">
-        <v>5.392314666666665</v>
+        <v>5.234121666666665</v>
       </c>
       <c r="P66">
-        <v>10.01429866666667</v>
+        <v>9.720511666666665</v>
       </c>
       <c r="Q66">
-        <v>49.01429866666666</v>
+        <v>48.72051166666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1084998394988209</v>
+        <v>0.1100003879404348</v>
       </c>
       <c r="T66">
-        <v>1.14836957969503</v>
+        <v>1.175852651374034</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.532608375001844</v>
+        <v>1.5090297846172</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07652513577915218</v>
+        <v>0.1045280349443</v>
       </c>
       <c r="C67">
-        <v>57.05479147153585</v>
+        <v>-124.7183776672972</v>
       </c>
       <c r="D67">
-        <v>370.6847914715358</v>
+        <v>193.9336223327028</v>
       </c>
       <c r="E67">
-        <v>101.13</v>
+        <v>106.152</v>
       </c>
       <c r="F67">
-        <v>326.43</v>
+        <v>331.452</v>
       </c>
       <c r="G67">
         <v>12.8</v>
@@ -6781,45 +6781,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M67">
-        <v>29.3787</v>
+        <v>48.6571536</v>
       </c>
       <c r="N67">
-        <v>14.95463333333333</v>
+        <v>-4.323820266666672</v>
       </c>
       <c r="O67">
-        <v>5.234121666666665</v>
+        <v>-1.513337093333335</v>
       </c>
       <c r="P67">
-        <v>9.720511666666665</v>
+        <v>-2.810483173333337</v>
       </c>
       <c r="Q67">
-        <v>48.72051166666667</v>
+        <v>36.18951682666666</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1100003879404348</v>
+        <v>0.113345352306874</v>
       </c>
       <c r="T67">
-        <v>1.175852651374034</v>
+        <v>1.237116848448332</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.35</v>
+        <v>0.3188979526880229</v>
       </c>
       <c r="W67">
-        <v>0.0585</v>
+        <v>0.09998578054539825</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.5090297846172</v>
+        <v>0.9111370076800656</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1045280349443</v>
+        <v>0.1055380349443</v>
       </c>
       <c r="C68">
-        <v>-124.7183776672972</v>
+        <v>-133.0192427779199</v>
       </c>
       <c r="D68">
-        <v>193.9336223327028</v>
+        <v>190.6547572220801</v>
       </c>
       <c r="E68">
-        <v>106.152</v>
+        <v>111.174</v>
       </c>
       <c r="F68">
-        <v>331.452</v>
+        <v>336.474</v>
       </c>
       <c r="G68">
         <v>12.8</v>
@@ -6863,37 +6863,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M68">
-        <v>48.6571536</v>
+        <v>49.3943832</v>
       </c>
       <c r="N68">
-        <v>-4.323820266666672</v>
+        <v>-5.061049866666671</v>
       </c>
       <c r="O68">
-        <v>-1.513337093333335</v>
+        <v>-1.771367453333335</v>
       </c>
       <c r="P68">
-        <v>-2.810483173333337</v>
+        <v>-3.289682413333336</v>
       </c>
       <c r="Q68">
-        <v>36.18951682666666</v>
+        <v>35.71031758666666</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.113345352306874</v>
+        <v>0.1153921811646581</v>
       </c>
       <c r="T68">
-        <v>1.237116848448332</v>
+        <v>1.274605237795251</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.3188979526880229</v>
+        <v>0.3141382817523808</v>
       </c>
       <c r="W68">
-        <v>0.09998578054539825</v>
+        <v>0.1006845002387505</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9111370076800656</v>
+        <v>0.8975379478639451</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1055380349443</v>
+        <v>0.1065480349443</v>
       </c>
       <c r="C69">
-        <v>-133.0192427779199</v>
+        <v>-141.2110787235743</v>
       </c>
       <c r="D69">
-        <v>190.6547572220801</v>
+        <v>187.4849212764257</v>
       </c>
       <c r="E69">
-        <v>111.174</v>
+        <v>116.196</v>
       </c>
       <c r="F69">
-        <v>336.474</v>
+        <v>341.496</v>
       </c>
       <c r="G69">
         <v>12.8</v>
@@ -6945,37 +6945,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M69">
-        <v>49.3943832</v>
+        <v>50.13161280000001</v>
       </c>
       <c r="N69">
-        <v>-5.061049866666671</v>
+        <v>-5.798279466666685</v>
       </c>
       <c r="O69">
-        <v>-1.771367453333335</v>
+        <v>-2.02939781333334</v>
       </c>
       <c r="P69">
-        <v>-3.289682413333336</v>
+        <v>-3.768881653333345</v>
       </c>
       <c r="Q69">
-        <v>35.71031758666666</v>
+        <v>35.23111834666665</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1153921811646581</v>
+        <v>0.1175669368260537</v>
       </c>
       <c r="T69">
-        <v>1.274605237795251</v>
+        <v>1.314436651476354</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.3141382817523808</v>
+        <v>0.3095186011383751</v>
       </c>
       <c r="W69">
-        <v>0.1006845002387505</v>
+        <v>0.1013626693528866</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8975379478639451</v>
+        <v>0.8843388603953575</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1065480349443</v>
+        <v>0.1075580349443001</v>
       </c>
       <c r="C70">
-        <v>-141.2110787235743</v>
+        <v>-149.2992347413293</v>
       </c>
       <c r="D70">
-        <v>187.4849212764257</v>
+        <v>184.4187652586707</v>
       </c>
       <c r="E70">
-        <v>116.196</v>
+        <v>121.218</v>
       </c>
       <c r="F70">
-        <v>341.496</v>
+        <v>346.518</v>
       </c>
       <c r="G70">
         <v>12.8</v>
@@ -7027,37 +7027,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M70">
-        <v>50.13161280000001</v>
+        <v>50.86884240000001</v>
       </c>
       <c r="N70">
-        <v>-5.798279466666685</v>
+        <v>-6.535509066666684</v>
       </c>
       <c r="O70">
-        <v>-2.02939781333334</v>
+        <v>-2.287428173333339</v>
       </c>
       <c r="P70">
-        <v>-3.768881653333345</v>
+        <v>-4.248080893333345</v>
       </c>
       <c r="Q70">
-        <v>35.23111834666665</v>
+        <v>34.75191910666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1175669368260537</v>
+        <v>0.1198819993043135</v>
       </c>
       <c r="T70">
-        <v>1.314436651476354</v>
+        <v>1.356837833782043</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.3095186011383751</v>
+        <v>0.3050328243102827</v>
       </c>
       <c r="W70">
-        <v>0.1013626693528866</v>
+        <v>0.1020211813912505</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8843388603953575</v>
+        <v>0.8715223551722364</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1075580349443001</v>
+        <v>0.1085680349443</v>
       </c>
       <c r="C71">
-        <v>-149.2992347413293</v>
+        <v>-157.2887157701132</v>
       </c>
       <c r="D71">
-        <v>184.4187652586707</v>
+        <v>181.4512842298869</v>
       </c>
       <c r="E71">
-        <v>121.218</v>
+        <v>126.24</v>
       </c>
       <c r="F71">
-        <v>346.518</v>
+        <v>351.54</v>
       </c>
       <c r="G71">
         <v>12.8</v>
@@ -7109,37 +7109,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M71">
-        <v>50.86884240000001</v>
+        <v>51.606072</v>
       </c>
       <c r="N71">
-        <v>-6.535509066666684</v>
+        <v>-7.272738666666676</v>
       </c>
       <c r="O71">
-        <v>-2.287428173333339</v>
+        <v>-2.545458533333337</v>
       </c>
       <c r="P71">
-        <v>-4.248080893333345</v>
+        <v>-4.727280133333339</v>
       </c>
       <c r="Q71">
-        <v>34.75191910666666</v>
+        <v>34.27271986666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1198819993043135</v>
+        <v>0.1223513992811239</v>
       </c>
       <c r="T71">
-        <v>1.356837833782043</v>
+        <v>1.402065761574777</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.3050328243102827</v>
+        <v>0.3006752125344216</v>
       </c>
       <c r="W71">
-        <v>0.1020211813912505</v>
+        <v>0.1026608787999469</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8715223551722364</v>
+        <v>0.8590720358126331</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1085680349443</v>
+        <v>0.1095780349443</v>
       </c>
       <c r="C72">
-        <v>-157.2887157701132</v>
+        <v>-165.1842097125378</v>
       </c>
       <c r="D72">
-        <v>181.4512842298869</v>
+        <v>178.5777902874622</v>
       </c>
       <c r="E72">
-        <v>126.24</v>
+        <v>131.262</v>
       </c>
       <c r="F72">
-        <v>351.54</v>
+        <v>356.562</v>
       </c>
       <c r="G72">
         <v>12.8</v>
@@ -7191,37 +7191,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M72">
-        <v>51.606072</v>
+        <v>52.3433016</v>
       </c>
       <c r="N72">
-        <v>-7.272738666666676</v>
+        <v>-8.009968266666675</v>
       </c>
       <c r="O72">
-        <v>-2.545458533333337</v>
+        <v>-2.803488893333336</v>
       </c>
       <c r="P72">
-        <v>-4.727280133333339</v>
+        <v>-5.206479373333339</v>
       </c>
       <c r="Q72">
-        <v>34.27271986666666</v>
+        <v>33.79352062666666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1223513992811239</v>
+        <v>0.1249911027046109</v>
       </c>
       <c r="T72">
-        <v>1.402065761574777</v>
+        <v>1.450412856801494</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.3006752125344216</v>
+        <v>0.2964403503860495</v>
       </c>
       <c r="W72">
-        <v>0.1026608787999469</v>
+        <v>0.1032825565633279</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8590720358126331</v>
+        <v>0.8469724296744271</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1095780349443</v>
+        <v>0.1105880349443</v>
       </c>
       <c r="C73">
-        <v>-165.1842097125376</v>
+        <v>-172.9901121467664</v>
       </c>
       <c r="D73">
-        <v>178.5777902874624</v>
+        <v>175.7938878532336</v>
       </c>
       <c r="E73">
-        <v>131.2619999999999</v>
+        <v>136.284</v>
       </c>
       <c r="F73">
-        <v>356.562</v>
+        <v>361.584</v>
       </c>
       <c r="G73">
         <v>12.8</v>
@@ -7273,37 +7273,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M73">
-        <v>52.3433016</v>
+        <v>53.0805312</v>
       </c>
       <c r="N73">
-        <v>-8.009968266666668</v>
+        <v>-8.747197866666674</v>
       </c>
       <c r="O73">
-        <v>-2.803488893333334</v>
+        <v>-3.061519253333336</v>
       </c>
       <c r="P73">
-        <v>-5.206479373333334</v>
+        <v>-5.685678613333339</v>
       </c>
       <c r="Q73">
-        <v>33.79352062666666</v>
+        <v>33.31432138666666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1249911027046109</v>
+        <v>0.1278193563726327</v>
       </c>
       <c r="T73">
-        <v>1.450412856801493</v>
+        <v>1.502213315972975</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2964403503860495</v>
+        <v>0.2923231232973543</v>
       </c>
       <c r="W73">
-        <v>0.1032825565633279</v>
+        <v>0.1038869654999484</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8469724296744272</v>
+        <v>0.8352089237067267</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1105880349443</v>
+        <v>0.1115980349443</v>
       </c>
       <c r="C74">
-        <v>-172.9901121467664</v>
+        <v>-180.7105487624202</v>
       </c>
       <c r="D74">
-        <v>175.7938878532336</v>
+        <v>173.0954512375797</v>
       </c>
       <c r="E74">
-        <v>136.284</v>
+        <v>141.306</v>
       </c>
       <c r="F74">
-        <v>361.584</v>
+        <v>366.606</v>
       </c>
       <c r="G74">
         <v>12.8</v>
@@ -7355,37 +7355,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M74">
-        <v>53.0805312</v>
+        <v>53.8177608</v>
       </c>
       <c r="N74">
-        <v>-8.747197866666674</v>
+        <v>-9.484427466666673</v>
       </c>
       <c r="O74">
-        <v>-3.061519253333336</v>
+        <v>-3.319549613333336</v>
       </c>
       <c r="P74">
-        <v>-5.685678613333339</v>
+        <v>-6.164877853333338</v>
       </c>
       <c r="Q74">
-        <v>33.31432138666666</v>
+        <v>32.83512214666666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1278193563726327</v>
+        <v>0.1308571103123599</v>
       </c>
       <c r="T74">
-        <v>1.502213315972975</v>
+        <v>1.557850846194196</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2923231232973543</v>
+        <v>0.2883186969508152</v>
       </c>
       <c r="W74">
-        <v>0.1038869654999484</v>
+        <v>0.1044748152876203</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8352089237067267</v>
+        <v>0.8237677055737579</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1115980349443</v>
+        <v>0.1126080349443</v>
       </c>
       <c r="C75">
-        <v>-180.7105487624202</v>
+        <v>-188.3493957613735</v>
       </c>
       <c r="D75">
-        <v>173.0954512375797</v>
+        <v>170.4786042386265</v>
       </c>
       <c r="E75">
-        <v>141.306</v>
+        <v>146.328</v>
       </c>
       <c r="F75">
-        <v>366.606</v>
+        <v>371.628</v>
       </c>
       <c r="G75">
         <v>12.8</v>
@@ -7437,37 +7437,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M75">
-        <v>53.8177608</v>
+        <v>54.5549904</v>
       </c>
       <c r="N75">
-        <v>-9.484427466666673</v>
+        <v>-10.22165706666667</v>
       </c>
       <c r="O75">
-        <v>-3.319549613333336</v>
+        <v>-3.577579973333335</v>
       </c>
       <c r="P75">
-        <v>-6.164877853333338</v>
+        <v>-6.644077093333337</v>
       </c>
       <c r="Q75">
-        <v>32.83512214666666</v>
+        <v>32.35592290666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1308571103123599</v>
+        <v>0.134128537632066</v>
       </c>
       <c r="T75">
-        <v>1.557850846194196</v>
+        <v>1.617768186432434</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2883186969508152</v>
+        <v>0.2844224983433718</v>
       </c>
       <c r="W75">
-        <v>0.1044748152876203</v>
+        <v>0.105046777243193</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8237677055737579</v>
+        <v>0.8126357095524909</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1126080349443</v>
+        <v>0.1136180349443</v>
       </c>
       <c r="C76">
-        <v>-188.3493957613735</v>
+        <v>-195.9102984356021</v>
       </c>
       <c r="D76">
-        <v>170.4786042386265</v>
+        <v>167.9397015643979</v>
       </c>
       <c r="E76">
-        <v>146.328</v>
+        <v>151.35</v>
       </c>
       <c r="F76">
-        <v>371.628</v>
+        <v>376.65</v>
       </c>
       <c r="G76">
         <v>12.8</v>
@@ -7519,37 +7519,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M76">
-        <v>54.5549904</v>
+        <v>55.29222</v>
       </c>
       <c r="N76">
-        <v>-10.22165706666667</v>
+        <v>-10.95888666666667</v>
       </c>
       <c r="O76">
-        <v>-3.577579973333335</v>
+        <v>-3.835610333333335</v>
       </c>
       <c r="P76">
-        <v>-6.644077093333337</v>
+        <v>-7.123276333333337</v>
       </c>
       <c r="Q76">
-        <v>32.35592290666666</v>
+        <v>31.87672366666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.134128537632066</v>
+        <v>0.1376616791373487</v>
       </c>
       <c r="T76">
-        <v>1.617768186432434</v>
+        <v>1.682478913889732</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2844224983433718</v>
+        <v>0.2806301983654602</v>
       </c>
       <c r="W76">
-        <v>0.105046777243193</v>
+        <v>0.1056034868799505</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8126357095524909</v>
+        <v>0.8018005667584577</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1136180349443</v>
+        <v>0.1573144257291902</v>
       </c>
       <c r="C77">
-        <v>-195.9102984356021</v>
+        <v>-266.7386618712779</v>
       </c>
       <c r="D77">
-        <v>167.9397015643979</v>
+        <v>102.1333381287221</v>
       </c>
       <c r="E77">
-        <v>151.35</v>
+        <v>156.372</v>
       </c>
       <c r="F77">
-        <v>376.65</v>
+        <v>381.672</v>
       </c>
       <c r="G77">
         <v>12.8</v>
@@ -7601,45 +7601,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M77">
-        <v>55.29222</v>
+        <v>76.63973759999999</v>
       </c>
       <c r="N77">
-        <v>-10.95888666666667</v>
+        <v>-32.30640426666666</v>
       </c>
       <c r="O77">
-        <v>-3.835610333333335</v>
+        <v>-11.30724149333333</v>
       </c>
       <c r="P77">
-        <v>-7.123276333333337</v>
+        <v>-20.99916277333333</v>
       </c>
       <c r="Q77">
-        <v>31.87672366666666</v>
+        <v>18.00083722666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1376616791373487</v>
+        <v>0.1483492107051139</v>
       </c>
       <c r="T77">
-        <v>1.682478913889732</v>
+        <v>1.878224807859408</v>
       </c>
       <c r="U77">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.2806301983654602</v>
+        <v>0.2024624190084214</v>
       </c>
       <c r="W77">
-        <v>0.1056034868799505</v>
+        <v>0.160145546263109</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.8018005667584577</v>
+        <v>0.5784640543097754</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1573144257291902</v>
+        <v>0.1588644257291902</v>
       </c>
       <c r="C78">
-        <v>-266.7386618712779</v>
+        <v>-273.1608076118903</v>
       </c>
       <c r="D78">
-        <v>102.1333381287221</v>
+        <v>100.7331923881097</v>
       </c>
       <c r="E78">
-        <v>156.372</v>
+        <v>161.394</v>
       </c>
       <c r="F78">
-        <v>381.672</v>
+        <v>386.694</v>
       </c>
       <c r="G78">
         <v>12.8</v>
@@ -7683,37 +7683,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M78">
-        <v>76.63973759999999</v>
+        <v>77.64815520000001</v>
       </c>
       <c r="N78">
-        <v>-32.30640426666666</v>
+        <v>-33.31482186666668</v>
       </c>
       <c r="O78">
-        <v>-11.30724149333333</v>
+        <v>-11.66018765333334</v>
       </c>
       <c r="P78">
-        <v>-20.99916277333333</v>
+        <v>-21.65463421333334</v>
       </c>
       <c r="Q78">
-        <v>18.00083722666667</v>
+        <v>17.34536578666666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1483492107051139</v>
+        <v>0.1528078720401188</v>
       </c>
       <c r="T78">
-        <v>1.878224807859408</v>
+        <v>1.959886756027209</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.2024624190084214</v>
+        <v>0.1998330369433769</v>
       </c>
       <c r="W78">
-        <v>0.160145546263109</v>
+        <v>0.1606735261817699</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5784640543097754</v>
+        <v>0.570951534123934</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1588644257291902</v>
+        <v>0.1604144257291902</v>
       </c>
       <c r="C79">
-        <v>-273.1608076118903</v>
+        <v>-279.545083322022</v>
       </c>
       <c r="D79">
-        <v>100.7331923881097</v>
+        <v>99.37091667797796</v>
       </c>
       <c r="E79">
-        <v>161.394</v>
+        <v>166.416</v>
       </c>
       <c r="F79">
-        <v>386.694</v>
+        <v>391.716</v>
       </c>
       <c r="G79">
         <v>12.8</v>
@@ -7765,37 +7765,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M79">
-        <v>77.64815520000001</v>
+        <v>78.65657280000001</v>
       </c>
       <c r="N79">
-        <v>-33.31482186666668</v>
+        <v>-34.32323946666668</v>
       </c>
       <c r="O79">
-        <v>-11.66018765333334</v>
+        <v>-12.01313381333334</v>
       </c>
       <c r="P79">
-        <v>-21.65463421333334</v>
+        <v>-22.31010565333334</v>
       </c>
       <c r="Q79">
-        <v>17.34536578666666</v>
+        <v>16.68989434666666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1528078720401188</v>
+        <v>0.1576718662237606</v>
       </c>
       <c r="T79">
-        <v>1.959886756027209</v>
+        <v>2.048972517664809</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1998330369433769</v>
+        <v>0.1972710749312823</v>
       </c>
       <c r="W79">
-        <v>0.1606735261817699</v>
+        <v>0.1611879681537985</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.570951534123934</v>
+        <v>0.5636316426608067</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1604144257291902</v>
+        <v>0.1619644257291902</v>
       </c>
       <c r="C80">
-        <v>-279.545083322022</v>
+        <v>-285.8930049187933</v>
       </c>
       <c r="D80">
-        <v>99.37091667797796</v>
+        <v>98.04499508120668</v>
       </c>
       <c r="E80">
-        <v>166.416</v>
+        <v>171.438</v>
       </c>
       <c r="F80">
-        <v>391.716</v>
+        <v>396.738</v>
       </c>
       <c r="G80">
         <v>12.8</v>
@@ -7847,37 +7847,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M80">
-        <v>78.65657280000001</v>
+        <v>79.66499040000001</v>
       </c>
       <c r="N80">
-        <v>-34.32323946666668</v>
+        <v>-35.33165706666668</v>
       </c>
       <c r="O80">
-        <v>-12.01313381333334</v>
+        <v>-12.36607997333334</v>
       </c>
       <c r="P80">
-        <v>-22.31010565333334</v>
+        <v>-22.96557709333334</v>
       </c>
       <c r="Q80">
-        <v>16.68989434666666</v>
+        <v>16.03442290666666</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1576718662237606</v>
+        <v>0.1629990979487016</v>
       </c>
       <c r="T80">
-        <v>2.048972517664809</v>
+        <v>2.14654263755361</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1972710749312823</v>
+        <v>0.1947739727169623</v>
       </c>
       <c r="W80">
-        <v>0.1611879681537985</v>
+        <v>0.161689386278434</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5636316426608067</v>
+        <v>0.5564970649056066</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1619644257291902</v>
+        <v>0.1635144257291902</v>
       </c>
       <c r="C81">
-        <v>-285.8930049187933</v>
+        <v>-292.2060084762119</v>
       </c>
       <c r="D81">
-        <v>98.04499508120668</v>
+        <v>96.75399152378809</v>
       </c>
       <c r="E81">
-        <v>171.438</v>
+        <v>176.46</v>
       </c>
       <c r="F81">
-        <v>396.738</v>
+        <v>401.76</v>
       </c>
       <c r="G81">
         <v>12.8</v>
@@ -7929,37 +7929,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M81">
-        <v>79.66499040000001</v>
+        <v>80.67340799999999</v>
       </c>
       <c r="N81">
-        <v>-35.33165706666668</v>
+        <v>-36.34007466666667</v>
       </c>
       <c r="O81">
-        <v>-12.36607997333334</v>
+        <v>-12.71902613333333</v>
       </c>
       <c r="P81">
-        <v>-22.96557709333334</v>
+        <v>-23.62104853333333</v>
       </c>
       <c r="Q81">
-        <v>16.03442290666666</v>
+        <v>15.37895146666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1629990979487016</v>
+        <v>0.1688590528461367</v>
       </c>
       <c r="T81">
-        <v>2.14654263755361</v>
+        <v>2.253869769431291</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1947739727169623</v>
+        <v>0.1923392980580003</v>
       </c>
       <c r="W81">
-        <v>0.161689386278434</v>
+        <v>0.1621782689499535</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5564970649056066</v>
+        <v>0.5495408515942866</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1635144257291902</v>
+        <v>0.1650644257291902</v>
       </c>
       <c r="C82">
-        <v>-292.2060084762119</v>
+        <v>-298.4854554135107</v>
       </c>
       <c r="D82">
-        <v>96.75399152378809</v>
+        <v>95.49654458648926</v>
       </c>
       <c r="E82">
-        <v>176.46</v>
+        <v>181.482</v>
       </c>
       <c r="F82">
-        <v>401.76</v>
+        <v>406.782</v>
       </c>
       <c r="G82">
         <v>12.8</v>
@@ -8011,37 +8011,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M82">
-        <v>80.67340799999999</v>
+        <v>81.68182560000001</v>
       </c>
       <c r="N82">
-        <v>-36.34007466666667</v>
+        <v>-37.34849226666668</v>
       </c>
       <c r="O82">
-        <v>-12.71902613333333</v>
+        <v>-13.07197229333334</v>
       </c>
       <c r="P82">
-        <v>-23.62104853333333</v>
+        <v>-24.27651997333334</v>
       </c>
       <c r="Q82">
-        <v>15.37895146666667</v>
+        <v>14.72348002666666</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1688590528461367</v>
+        <v>0.1753358451011965</v>
       </c>
       <c r="T82">
-        <v>2.253869769431291</v>
+        <v>2.372494494138201</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1923392980580003</v>
+        <v>0.1899647388227163</v>
       </c>
       <c r="W82">
-        <v>0.1621782689499535</v>
+        <v>0.1626550804443986</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5495408515942866</v>
+        <v>0.5427563966363322</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1650644257291902</v>
+        <v>0.1666144257291902</v>
       </c>
       <c r="C83">
-        <v>-298.4854554135107</v>
+        <v>-304.7326372841</v>
       </c>
       <c r="D83">
-        <v>95.49654458648926</v>
+        <v>94.27136271590001</v>
       </c>
       <c r="E83">
-        <v>181.482</v>
+        <v>186.504</v>
       </c>
       <c r="F83">
-        <v>406.782</v>
+        <v>411.804</v>
       </c>
       <c r="G83">
         <v>12.8</v>
@@ -8093,37 +8093,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M83">
-        <v>81.68182560000001</v>
+        <v>82.69024320000001</v>
       </c>
       <c r="N83">
-        <v>-37.34849226666668</v>
+        <v>-38.35690986666668</v>
       </c>
       <c r="O83">
-        <v>-13.07197229333334</v>
+        <v>-13.42491845333334</v>
       </c>
       <c r="P83">
-        <v>-24.27651997333334</v>
+        <v>-24.93199141333334</v>
       </c>
       <c r="Q83">
-        <v>14.72348002666666</v>
+        <v>14.06800858666666</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1753358451011965</v>
+        <v>0.1825322809401519</v>
       </c>
       <c r="T83">
-        <v>2.372494494138201</v>
+        <v>2.504299743812545</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1899647388227163</v>
+        <v>0.1876480956663417</v>
       </c>
       <c r="W83">
-        <v>0.1626550804443986</v>
+        <v>0.1631202623901986</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5427563966363322</v>
+        <v>0.5361374161895478</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1666144257291902</v>
+        <v>0.1681644257291902</v>
       </c>
       <c r="C84">
-        <v>-304.7326372841</v>
+        <v>-310.9487802005472</v>
       </c>
       <c r="D84">
-        <v>94.27136271590001</v>
+        <v>93.07721979945279</v>
       </c>
       <c r="E84">
-        <v>186.504</v>
+        <v>191.526</v>
       </c>
       <c r="F84">
-        <v>411.804</v>
+        <v>416.826</v>
       </c>
       <c r="G84">
         <v>12.8</v>
@@ -8175,37 +8175,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M84">
-        <v>82.69024320000001</v>
+        <v>83.69866080000001</v>
       </c>
       <c r="N84">
-        <v>-38.35690986666668</v>
+        <v>-39.36532746666668</v>
       </c>
       <c r="O84">
-        <v>-13.42491845333334</v>
+        <v>-13.77786461333334</v>
       </c>
       <c r="P84">
-        <v>-24.93199141333334</v>
+        <v>-25.58746285333335</v>
       </c>
       <c r="Q84">
-        <v>14.06800858666666</v>
+        <v>13.41253714666665</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1825322809401519</v>
+        <v>0.1905753562895726</v>
       </c>
       <c r="T84">
-        <v>2.504299743812545</v>
+        <v>2.651611493448577</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1876480956663417</v>
+        <v>0.1853872752366267</v>
       </c>
       <c r="W84">
-        <v>0.1631202623901986</v>
+        <v>0.1635742351324853</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5361374161895478</v>
+        <v>0.529677929247505</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1681644257291902</v>
+        <v>0.1697144257291902</v>
       </c>
       <c r="C85">
-        <v>-310.9487802005472</v>
+        <v>-317.1350489274544</v>
       </c>
       <c r="D85">
-        <v>93.07721979945279</v>
+        <v>91.91295107254564</v>
       </c>
       <c r="E85">
-        <v>191.526</v>
+        <v>196.548</v>
       </c>
       <c r="F85">
-        <v>416.826</v>
+        <v>421.848</v>
       </c>
       <c r="G85">
         <v>12.8</v>
@@ -8257,37 +8257,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M85">
-        <v>83.69866080000001</v>
+        <v>84.7070784</v>
       </c>
       <c r="N85">
-        <v>-39.36532746666668</v>
+        <v>-40.37374506666667</v>
       </c>
       <c r="O85">
-        <v>-13.77786461333334</v>
+        <v>-14.13081077333333</v>
       </c>
       <c r="P85">
-        <v>-25.58746285333335</v>
+        <v>-26.24293429333334</v>
       </c>
       <c r="Q85">
-        <v>13.41253714666665</v>
+        <v>12.75706570666666</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1905753562895726</v>
+        <v>0.1996238160576709</v>
       </c>
       <c r="T85">
-        <v>2.651611493448577</v>
+        <v>2.817337211789114</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1853872752366267</v>
+        <v>0.1831802838647622</v>
       </c>
       <c r="W85">
-        <v>0.1635742351324853</v>
+        <v>0.1640173989999558</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.529677929247505</v>
+        <v>0.5233722396136062</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1697144257291902</v>
+        <v>0.1712644257291902</v>
       </c>
       <c r="C86">
-        <v>-317.1350489274543</v>
+        <v>-323.2925506709522</v>
       </c>
       <c r="D86">
-        <v>91.91295107254564</v>
+        <v>90.77744932904784</v>
       </c>
       <c r="E86">
-        <v>196.5479999999999</v>
+        <v>201.57</v>
       </c>
       <c r="F86">
-        <v>421.848</v>
+        <v>426.87</v>
       </c>
       <c r="G86">
         <v>12.8</v>
@@ -8339,37 +8339,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M86">
-        <v>84.7070784</v>
+        <v>85.715496</v>
       </c>
       <c r="N86">
-        <v>-40.37374506666667</v>
+        <v>-41.38216266666667</v>
       </c>
       <c r="O86">
-        <v>-14.13081077333333</v>
+        <v>-14.48375693333333</v>
       </c>
       <c r="P86">
-        <v>-26.24293429333334</v>
+        <v>-26.89840573333334</v>
       </c>
       <c r="Q86">
-        <v>12.75706570666666</v>
+        <v>12.10159426666666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1996238160576708</v>
+        <v>0.2098787371281822</v>
       </c>
       <c r="T86">
-        <v>2.817337211789112</v>
+        <v>3.005159692575053</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1831802838647622</v>
+        <v>0.1810252217016473</v>
       </c>
       <c r="W86">
-        <v>0.1640173989999558</v>
+        <v>0.1644501354823092</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5233722396136062</v>
+        <v>0.5172149191475638</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1712644257291902</v>
+        <v>0.1728144257291902</v>
       </c>
       <c r="C87">
-        <v>-323.2925506709522</v>
+        <v>-329.4223385907277</v>
       </c>
       <c r="D87">
-        <v>90.77744932904784</v>
+        <v>89.66966140927232</v>
       </c>
       <c r="E87">
-        <v>201.57</v>
+        <v>206.592</v>
       </c>
       <c r="F87">
-        <v>426.87</v>
+        <v>431.892</v>
       </c>
       <c r="G87">
         <v>12.8</v>
@@ -8421,37 +8421,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M87">
-        <v>85.715496</v>
+        <v>86.7239136</v>
       </c>
       <c r="N87">
-        <v>-41.38216266666667</v>
+        <v>-42.39058026666667</v>
       </c>
       <c r="O87">
-        <v>-14.48375693333333</v>
+        <v>-14.83670309333334</v>
       </c>
       <c r="P87">
-        <v>-26.89840573333334</v>
+        <v>-27.55387717333334</v>
       </c>
       <c r="Q87">
-        <v>12.10159426666666</v>
+        <v>11.44612282666666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2098787371281822</v>
+        <v>0.2215986469230524</v>
       </c>
       <c r="T87">
-        <v>3.005159692575053</v>
+        <v>3.219813956330414</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1810252217016473</v>
+        <v>0.1789202772632561</v>
       </c>
       <c r="W87">
-        <v>0.1644501354823092</v>
+        <v>0.1648728083255382</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5172149191475638</v>
+        <v>0.5112007921807317</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1728144257291902</v>
+        <v>0.1743644257291902</v>
       </c>
       <c r="C88">
-        <v>-329.4223385907277</v>
+        <v>-335.5254150580013</v>
       </c>
       <c r="D88">
-        <v>89.66966140927232</v>
+        <v>88.5885849419987</v>
       </c>
       <c r="E88">
-        <v>206.592</v>
+        <v>211.614</v>
       </c>
       <c r="F88">
-        <v>431.892</v>
+        <v>436.914</v>
       </c>
       <c r="G88">
         <v>12.8</v>
@@ -8503,37 +8503,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M88">
-        <v>86.7239136</v>
+        <v>87.7323312</v>
       </c>
       <c r="N88">
-        <v>-42.39058026666667</v>
+        <v>-43.39899786666668</v>
       </c>
       <c r="O88">
-        <v>-14.83670309333334</v>
+        <v>-15.18964925333334</v>
       </c>
       <c r="P88">
-        <v>-27.55387717333334</v>
+        <v>-28.20934861333334</v>
       </c>
       <c r="Q88">
-        <v>11.44612282666666</v>
+        <v>10.79065138666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2215986469230524</v>
+        <v>0.2351216197632872</v>
       </c>
       <c r="T88">
-        <v>3.219813956330414</v>
+        <v>3.467491952971215</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1789202772632561</v>
+        <v>0.1768637223521842</v>
       </c>
       <c r="W88">
-        <v>0.1648728083255382</v>
+        <v>0.1652857645516814</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5112007921807317</v>
+        <v>0.5053249210062405</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1743644257291902</v>
+        <v>0.2073787642970887</v>
       </c>
       <c r="C89">
-        <v>-335.5254150580013</v>
+        <v>-358.6481447501077</v>
       </c>
       <c r="D89">
-        <v>88.5885849419987</v>
+        <v>70.48785524989225</v>
       </c>
       <c r="E89">
-        <v>211.614</v>
+        <v>216.636</v>
       </c>
       <c r="F89">
-        <v>436.914</v>
+        <v>441.936</v>
       </c>
       <c r="G89">
         <v>12.8</v>
@@ -8585,45 +8585,45 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M89">
-        <v>87.7323312</v>
+        <v>104.2085088</v>
       </c>
       <c r="N89">
-        <v>-43.39899786666668</v>
+        <v>-59.87517546666668</v>
       </c>
       <c r="O89">
-        <v>-15.18964925333334</v>
+        <v>-20.95631141333334</v>
       </c>
       <c r="P89">
-        <v>-28.20934861333334</v>
+        <v>-38.91886405333334</v>
       </c>
       <c r="Q89">
-        <v>10.79065138666666</v>
+        <v>0.08113594666666302</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2351216197632872</v>
+        <v>0.2564345761427156</v>
       </c>
       <c r="T89">
-        <v>3.467491952971215</v>
+        <v>3.857846233861568</v>
       </c>
       <c r="U89">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1768637223521842</v>
+        <v>0.1489001891049674</v>
       </c>
       <c r="W89">
-        <v>0.1652857645516814</v>
+        <v>0.2006893354090487</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.5053249210062405</v>
+        <v>0.4254291117284784</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2073787642970887</v>
+        <v>0.2092787642970887</v>
       </c>
       <c r="C90">
-        <v>-358.6481447501077</v>
+        <v>-364.4893760768837</v>
       </c>
       <c r="D90">
-        <v>70.48785524989225</v>
+        <v>69.66862392311633</v>
       </c>
       <c r="E90">
-        <v>216.636</v>
+        <v>221.658</v>
       </c>
       <c r="F90">
-        <v>441.936</v>
+        <v>446.958</v>
       </c>
       <c r="G90">
         <v>12.8</v>
@@ -8667,37 +8667,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M90">
-        <v>104.2085088</v>
+        <v>105.3926964</v>
       </c>
       <c r="N90">
-        <v>-59.87517546666668</v>
+        <v>-61.05936306666666</v>
       </c>
       <c r="O90">
-        <v>-20.95631141333334</v>
+        <v>-21.37077707333333</v>
       </c>
       <c r="P90">
-        <v>-38.91886405333334</v>
+        <v>-39.68858599333333</v>
       </c>
       <c r="Q90">
-        <v>0.08113594666666302</v>
+        <v>-0.6885859933333336</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2564345761427156</v>
+        <v>0.2755831739738716</v>
       </c>
       <c r="T90">
-        <v>3.857846233861568</v>
+        <v>4.208559527848982</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1489001891049674</v>
+        <v>0.1472271532723274</v>
       </c>
       <c r="W90">
-        <v>0.2006893354090487</v>
+        <v>0.2010838372583852</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4254291117284784</v>
+        <v>0.4206490093495068</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2092787642970887</v>
+        <v>0.2111787642970887</v>
       </c>
       <c r="C91">
-        <v>-364.4893760768837</v>
+        <v>-370.3117834690694</v>
       </c>
       <c r="D91">
-        <v>69.66862392311633</v>
+        <v>68.86821653093064</v>
       </c>
       <c r="E91">
-        <v>221.658</v>
+        <v>226.68</v>
       </c>
       <c r="F91">
-        <v>446.958</v>
+        <v>451.98</v>
       </c>
       <c r="G91">
         <v>12.8</v>
@@ -8749,37 +8749,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M91">
-        <v>105.3926964</v>
+        <v>106.576884</v>
       </c>
       <c r="N91">
-        <v>-61.05936306666666</v>
+        <v>-62.24355066666668</v>
       </c>
       <c r="O91">
-        <v>-21.37077707333333</v>
+        <v>-21.78524273333334</v>
       </c>
       <c r="P91">
-        <v>-39.68858599333333</v>
+        <v>-40.45830793333334</v>
       </c>
       <c r="Q91">
-        <v>-0.6885859933333336</v>
+        <v>-1.458307933333344</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2755831739738716</v>
+        <v>0.2985614913712588</v>
       </c>
       <c r="T91">
-        <v>4.208559527848982</v>
+        <v>4.629415480633881</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1472271532723274</v>
+        <v>0.1455912960137459</v>
       </c>
       <c r="W91">
-        <v>0.2010838372583852</v>
+        <v>0.2014695723999587</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4206490093495068</v>
+        <v>0.4159751314678456</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2111787642970887</v>
+        <v>0.2130787642970887</v>
       </c>
       <c r="C92">
-        <v>-370.3117834690694</v>
+        <v>-376.1160083495472</v>
       </c>
       <c r="D92">
-        <v>68.86821653093064</v>
+        <v>68.08599165045281</v>
       </c>
       <c r="E92">
-        <v>226.68</v>
+        <v>231.702</v>
       </c>
       <c r="F92">
-        <v>451.98</v>
+        <v>457.002</v>
       </c>
       <c r="G92">
         <v>12.8</v>
@@ -8831,37 +8831,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M92">
-        <v>106.576884</v>
+        <v>107.7610716</v>
       </c>
       <c r="N92">
-        <v>-62.24355066666668</v>
+        <v>-63.42773826666668</v>
       </c>
       <c r="O92">
-        <v>-21.78524273333334</v>
+        <v>-22.19970839333334</v>
       </c>
       <c r="P92">
-        <v>-40.45830793333334</v>
+        <v>-41.22802987333334</v>
       </c>
       <c r="Q92">
-        <v>-1.458307933333344</v>
+        <v>-2.228029873333341</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2985614913712588</v>
+        <v>0.3266461015236209</v>
       </c>
       <c r="T92">
-        <v>4.629415480633881</v>
+        <v>5.143794978482092</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1455912960137459</v>
+        <v>0.1439913916619465</v>
       </c>
       <c r="W92">
-        <v>0.2014695723999587</v>
+        <v>0.201846829846113</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4159751314678456</v>
+        <v>0.4114039761769901</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2130787642970887</v>
+        <v>0.2149787642970887</v>
       </c>
       <c r="C93">
-        <v>-376.1160083495472</v>
+        <v>-381.9026633266263</v>
       </c>
       <c r="D93">
-        <v>68.08599165045281</v>
+        <v>67.32133667337372</v>
       </c>
       <c r="E93">
-        <v>231.702</v>
+        <v>236.724</v>
       </c>
       <c r="F93">
-        <v>457.002</v>
+        <v>462.024</v>
       </c>
       <c r="G93">
         <v>12.8</v>
@@ -8913,37 +8913,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M93">
-        <v>107.7610716</v>
+        <v>108.9452592</v>
       </c>
       <c r="N93">
-        <v>-63.42773826666668</v>
+        <v>-64.61192586666668</v>
       </c>
       <c r="O93">
-        <v>-22.19970839333334</v>
+        <v>-22.61417405333334</v>
       </c>
       <c r="P93">
-        <v>-41.22802987333334</v>
+        <v>-41.99775181333334</v>
       </c>
       <c r="Q93">
-        <v>-2.228029873333341</v>
+        <v>-2.997751813333345</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3266461015236209</v>
+        <v>0.3617518642140736</v>
       </c>
       <c r="T93">
-        <v>5.143794978482092</v>
+        <v>5.786769350792355</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1439913916619465</v>
+        <v>0.1424262678395341</v>
       </c>
       <c r="W93">
-        <v>0.201846829846113</v>
+        <v>0.2022158860434379</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4114039761769901</v>
+        <v>0.4069321938272402</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2149787642970887</v>
+        <v>0.2168787642970887</v>
       </c>
       <c r="C94">
-        <v>-381.9026633266263</v>
+        <v>-387.672333794115</v>
       </c>
       <c r="D94">
-        <v>67.32133667337372</v>
+        <v>66.57366620588493</v>
       </c>
       <c r="E94">
-        <v>236.724</v>
+        <v>241.746</v>
       </c>
       <c r="F94">
-        <v>462.024</v>
+        <v>467.046</v>
       </c>
       <c r="G94">
         <v>12.8</v>
@@ -8995,37 +8995,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M94">
-        <v>108.9452592</v>
+        <v>110.1294468</v>
       </c>
       <c r="N94">
-        <v>-64.61192586666668</v>
+        <v>-65.79611346666667</v>
       </c>
       <c r="O94">
-        <v>-22.61417405333334</v>
+        <v>-23.02863971333333</v>
       </c>
       <c r="P94">
-        <v>-41.99775181333334</v>
+        <v>-42.76747375333333</v>
       </c>
       <c r="Q94">
-        <v>-2.997751813333345</v>
+        <v>-3.767473753333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3617518642140736</v>
+        <v>0.4068878448160842</v>
       </c>
       <c r="T94">
-        <v>5.786769350792355</v>
+        <v>6.613450686619834</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1424262678395341</v>
+        <v>0.1408948025939477</v>
       </c>
       <c r="W94">
-        <v>0.2022158860434379</v>
+        <v>0.2025770055483471</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4069321938272402</v>
+        <v>0.4025565788398506</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2168787642970887</v>
+        <v>0.2187787642970887</v>
       </c>
       <c r="C95">
-        <v>-387.672333794115</v>
+        <v>-393.4255794259427</v>
       </c>
       <c r="D95">
-        <v>66.57366620588493</v>
+        <v>65.84242057405736</v>
       </c>
       <c r="E95">
-        <v>241.746</v>
+        <v>246.768</v>
       </c>
       <c r="F95">
-        <v>467.046</v>
+        <v>472.068</v>
       </c>
       <c r="G95">
         <v>12.8</v>
@@ -9077,37 +9077,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M95">
-        <v>110.1294468</v>
+        <v>111.3136344</v>
       </c>
       <c r="N95">
-        <v>-65.79611346666667</v>
+        <v>-66.98030106666668</v>
       </c>
       <c r="O95">
-        <v>-23.02863971333333</v>
+        <v>-23.44310537333334</v>
       </c>
       <c r="P95">
-        <v>-42.76747375333333</v>
+        <v>-43.53719569333335</v>
       </c>
       <c r="Q95">
-        <v>-3.767473753333334</v>
+        <v>-4.537195693333345</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4068878448160842</v>
+        <v>0.4670691522854317</v>
       </c>
       <c r="T95">
-        <v>6.613450686619834</v>
+        <v>7.715692467723142</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1408948025939477</v>
+        <v>0.1393959217152886</v>
       </c>
       <c r="W95">
-        <v>0.2025770055483471</v>
+        <v>0.2029304416595349</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4025565788398506</v>
+        <v>0.3982740620436819</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2187787642970887</v>
+        <v>0.2206787642970887</v>
       </c>
       <c r="C96">
-        <v>-393.4255794259427</v>
+        <v>-399.1629355733488</v>
       </c>
       <c r="D96">
-        <v>65.84242057405736</v>
+        <v>65.1270644266512</v>
       </c>
       <c r="E96">
-        <v>246.768</v>
+        <v>251.79</v>
       </c>
       <c r="F96">
-        <v>472.068</v>
+        <v>477.09</v>
       </c>
       <c r="G96">
         <v>12.8</v>
@@ -9159,37 +9159,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M96">
-        <v>111.3136344</v>
+        <v>112.497822</v>
       </c>
       <c r="N96">
-        <v>-66.98030106666668</v>
+        <v>-68.16448866666668</v>
       </c>
       <c r="O96">
-        <v>-23.44310537333334</v>
+        <v>-23.85757103333334</v>
       </c>
       <c r="P96">
-        <v>-43.53719569333335</v>
+        <v>-44.30691763333334</v>
       </c>
       <c r="Q96">
-        <v>-4.537195693333345</v>
+        <v>-5.306917633333342</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4670691522854317</v>
+        <v>0.5513229827425181</v>
       </c>
       <c r="T96">
-        <v>7.715692467723142</v>
+        <v>9.258830961267774</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1393959217152886</v>
+        <v>0.1379285962235488</v>
       </c>
       <c r="W96">
-        <v>0.2029304416595349</v>
+        <v>0.2032764370104872</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3982740620436819</v>
+        <v>0.3940817034958537</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2206787642970887</v>
+        <v>0.2225787642970887</v>
       </c>
       <c r="C97">
-        <v>-399.1629355733488</v>
+        <v>-404.8849145719727</v>
       </c>
       <c r="D97">
-        <v>65.1270644266512</v>
+        <v>64.42708542802735</v>
       </c>
       <c r="E97">
-        <v>251.79</v>
+        <v>256.812</v>
       </c>
       <c r="F97">
-        <v>477.09</v>
+        <v>482.112</v>
       </c>
       <c r="G97">
         <v>12.8</v>
@@ -9241,37 +9241,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M97">
-        <v>112.497822</v>
+        <v>113.6820096</v>
       </c>
       <c r="N97">
-        <v>-68.16448866666668</v>
+        <v>-69.34867626666669</v>
       </c>
       <c r="O97">
-        <v>-23.85757103333334</v>
+        <v>-24.27203669333334</v>
       </c>
       <c r="P97">
-        <v>-44.30691763333334</v>
+        <v>-45.07663957333335</v>
       </c>
       <c r="Q97">
-        <v>-5.306917633333342</v>
+        <v>-6.076639573333352</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5513229827425181</v>
+        <v>0.6777037284281479</v>
       </c>
       <c r="T97">
-        <v>9.258830961267774</v>
+        <v>11.57353870158472</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1379285962235488</v>
+        <v>0.1364918400128868</v>
       </c>
       <c r="W97">
-        <v>0.2032764370104872</v>
+        <v>0.2036152241249613</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3940817034958537</v>
+        <v>0.3899766857511052</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2225787642970887</v>
+        <v>0.2244787642970887</v>
       </c>
       <c r="C98">
-        <v>-404.8849145719726</v>
+        <v>-410.5920069655472</v>
       </c>
       <c r="D98">
-        <v>64.42708542802735</v>
+        <v>63.74199303445271</v>
       </c>
       <c r="E98">
-        <v>256.812</v>
+        <v>261.8339999999999</v>
       </c>
       <c r="F98">
-        <v>482.112</v>
+        <v>487.134</v>
       </c>
       <c r="G98">
         <v>12.8</v>
@@ -9323,37 +9323,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M98">
-        <v>113.6820096</v>
+        <v>114.8661972</v>
       </c>
       <c r="N98">
-        <v>-69.34867626666667</v>
+        <v>-70.53286386666666</v>
       </c>
       <c r="O98">
-        <v>-24.27203669333333</v>
+        <v>-24.68650235333333</v>
       </c>
       <c r="P98">
-        <v>-45.07663957333334</v>
+        <v>-45.84636151333333</v>
       </c>
       <c r="Q98">
-        <v>-6.076639573333338</v>
+        <v>-6.846361513333335</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6777037284281463</v>
+        <v>0.8883383045708617</v>
       </c>
       <c r="T98">
-        <v>11.57353870158469</v>
+        <v>15.43138493544626</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1364918400128868</v>
+        <v>0.1350847076416199</v>
       </c>
       <c r="W98">
-        <v>0.2036152241249613</v>
+        <v>0.203947025938106</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3899766857511052</v>
+        <v>0.3859563075474857</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2244787642970887</v>
+        <v>0.2263787642970887</v>
       </c>
       <c r="C99">
-        <v>-410.5920069655472</v>
+        <v>-416.2846826523418</v>
       </c>
       <c r="D99">
-        <v>63.74199303445271</v>
+        <v>63.07131734765821</v>
       </c>
       <c r="E99">
-        <v>261.8339999999999</v>
+        <v>266.856</v>
       </c>
       <c r="F99">
-        <v>487.134</v>
+        <v>492.156</v>
       </c>
       <c r="G99">
         <v>12.8</v>
@@ -9405,37 +9405,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M99">
-        <v>114.8661972</v>
+        <v>116.0503848</v>
       </c>
       <c r="N99">
-        <v>-70.53286386666666</v>
+        <v>-71.71705146666667</v>
       </c>
       <c r="O99">
-        <v>-24.68650235333333</v>
+        <v>-25.10096801333334</v>
       </c>
       <c r="P99">
-        <v>-45.84636151333333</v>
+        <v>-46.61608345333334</v>
       </c>
       <c r="Q99">
-        <v>-6.846361513333335</v>
+        <v>-7.616083453333339</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8883383045708617</v>
+        <v>1.309607456856293</v>
       </c>
       <c r="T99">
-        <v>15.43138493544626</v>
+        <v>23.14707740316938</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1350847076416199</v>
+        <v>0.1337062922575218</v>
       </c>
       <c r="W99">
-        <v>0.203947025938106</v>
+        <v>0.2042720562856764</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3859563075474857</v>
+        <v>0.3820179778786337</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2263787642970887</v>
+        <v>0.2282787642970887</v>
       </c>
       <c r="C100">
-        <v>-416.2846826523418</v>
+        <v>-421.9633919599819</v>
       </c>
       <c r="D100">
-        <v>63.07131734765821</v>
+        <v>62.41460804001812</v>
       </c>
       <c r="E100">
-        <v>266.856</v>
+        <v>271.878</v>
       </c>
       <c r="F100">
-        <v>492.156</v>
+        <v>497.178</v>
       </c>
       <c r="G100">
         <v>12.8</v>
@@ -9487,37 +9487,37 @@
         <v>44.33333333333333</v>
       </c>
       <c r="M100">
-        <v>116.0503848</v>
+        <v>117.2345724</v>
       </c>
       <c r="N100">
-        <v>-71.71705146666667</v>
+        <v>-72.90123906666668</v>
       </c>
       <c r="O100">
-        <v>-25.10096801333334</v>
+        <v>-25.51543367333333</v>
       </c>
       <c r="P100">
-        <v>-46.61608345333334</v>
+        <v>-47.38580539333334</v>
       </c>
       <c r="Q100">
-        <v>-7.616083453333339</v>
+        <v>-8.385805393333342</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.309607456856293</v>
+        <v>2.573414913712585</v>
       </c>
       <c r="T100">
-        <v>23.14707740316938</v>
+        <v>46.29415480633877</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1337062922575218</v>
+        <v>0.1323557236488599</v>
       </c>
       <c r="W100">
-        <v>0.2042720562856764</v>
+        <v>0.2045905203635988</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3820179778786337</v>
+        <v>0.3781592104253142</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2282787642970887</v>
-      </c>
-      <c r="C101">
-        <v>-421.9633919599819</v>
-      </c>
-      <c r="D101">
-        <v>62.41460804001812</v>
-      </c>
-      <c r="E101">
-        <v>271.878</v>
-      </c>
-      <c r="F101">
-        <v>497.178</v>
-      </c>
-      <c r="G101">
-        <v>12.8</v>
-      </c>
-      <c r="H101">
-        <v>276.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>83.33333333333333</v>
-      </c>
-      <c r="K101">
-        <v>39</v>
-      </c>
-      <c r="L101">
-        <v>44.33333333333333</v>
-      </c>
-      <c r="M101">
-        <v>117.2345724</v>
-      </c>
-      <c r="N101">
-        <v>-72.90123906666668</v>
-      </c>
-      <c r="O101">
-        <v>-25.51543367333333</v>
-      </c>
-      <c r="P101">
-        <v>-47.38580539333334</v>
-      </c>
-      <c r="Q101">
-        <v>-8.385805393333342</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.573414913712585</v>
-      </c>
-      <c r="T101">
-        <v>46.29415480633877</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1323557236488599</v>
-      </c>
-      <c r="W101">
-        <v>0.2045905203635988</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3781592104253142</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
